--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_38.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_38.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3938319.10081791</v>
+        <v>3978324.353445381</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3629416.628852692</v>
+        <v>3629416.628852691</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3629416.628852692</v>
+        <v>3629416.628852691</v>
       </c>
     </row>
     <row r="11">
@@ -654,13 +654,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>481.9993129555745</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
         <v>49.47457824299391</v>
       </c>
       <c r="D2" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E2" t="n">
         <v>4.363289606868648</v>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>403.7573722870162</v>
       </c>
       <c r="H2" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I2" t="n">
         <v>150.0811596826846</v>
@@ -702,22 +702,22 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>481.0251995050527</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U2" t="n">
         <v>249.2212965486107</v>
       </c>
       <c r="V2" t="n">
-        <v>629.8510241668239</v>
+        <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>238.3734759809475</v>
+        <v>373.6719088553828</v>
       </c>
       <c r="X2" t="n">
         <v>192.2818334606677</v>
@@ -733,7 +733,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>284.6463592929432</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -790,10 +790,10 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>400.2103597601867</v>
+        <v>0.2103597601867477</v>
       </c>
       <c r="V3" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W3" t="n">
         <v>32.37314290982852</v>
@@ -802,7 +802,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y3" t="n">
-        <v>73.16906773709604</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -891,7 +891,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>367.3789055126944</v>
+        <v>81.99931295557451</v>
       </c>
       <c r="C5" t="n">
         <v>49.47457824299391</v>
@@ -906,13 +906,13 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G5" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W5" t="n">
-        <v>238.3734759809475</v>
+        <v>373.6719088553828</v>
       </c>
       <c r="X5" t="n">
         <v>192.2818334606677</v>
@@ -979,7 +979,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -988,7 +988,7 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -1024,7 +1024,7 @@
         <v>66.5639999646113</v>
       </c>
       <c r="T6" t="n">
-        <v>5.357765217513816</v>
+        <v>182.9776155168127</v>
       </c>
       <c r="U6" t="n">
         <v>0.2103597601867477</v>
@@ -1036,7 +1036,7 @@
         <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
-        <v>186.9785797091949</v>
+        <v>19.86273944538755</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
@@ -1137,7 +1137,7 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>140.6214809922826</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F8" t="n">
         <v>404.8896287080119</v>
@@ -1146,7 +1146,7 @@
         <v>403.7573722870162</v>
       </c>
       <c r="H8" t="n">
-        <v>8.009658703527407</v>
+        <v>408.0096587035274</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -1179,10 +1179,10 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T8" t="n">
-        <v>586.6755817285639</v>
+        <v>322.9337731139789</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1210,13 +1210,13 @@
         <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>167.1158402638074</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>414.5106671915202</v>
       </c>
       <c r="W9" t="n">
-        <v>32.37314290982852</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X9" t="n">
-        <v>19.86273944538755</v>
+        <v>77.5883638288102</v>
       </c>
       <c r="Y9" t="n">
         <v>0</v>
@@ -1374,13 +1374,13 @@
         <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
         <v>183.0096587035274</v>
@@ -1416,22 +1416,22 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>114.4420741331353</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>410.5297235614264</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>413.3734759809475</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>367.2818334606677</v>
       </c>
       <c r="Y11" t="n">
         <v>286.3174326828064</v>
@@ -1526,10 +1526,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>60.53621805555548</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1553,7 +1553,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>198.5476281577792</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
@@ -1562,10 +1562,10 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>33.96770662714829</v>
       </c>
       <c r="P13" t="n">
-        <v>345.9207354288559</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1787,10 +1787,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>12.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>147.5476281577792</v>
       </c>
       <c r="M16" t="n">
         <v>0</v>
@@ -1799,10 +1799,10 @@
         <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>342.4496984536982</v>
+        <v>364.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>411.4478973282775</v>
+        <v>143.0101500411831</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1811,7 +1811,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>86.37347970285543</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1857,7 +1857,7 @@
         <v>127.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>132.2678500889416</v>
+        <v>132.0096587035274</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1896,7 +1896,7 @@
         <v>310.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>373.2212965486107</v>
+        <v>373.4794879340254</v>
       </c>
       <c r="V17" t="n">
         <v>353.8510241668239</v>
@@ -2033,16 +2033,16 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>295.1850752716849</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>411.4478973282775</v>
+        <v>8.873254084692784</v>
       </c>
       <c r="Q19" t="n">
-        <v>342.4496984536982</v>
+        <v>449.839266425598</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
@@ -2082,10 +2082,10 @@
         <v>173.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>134.597347125264</v>
+        <v>134.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>128.3632896068686</v>
+        <v>128.6214809922828</v>
       </c>
       <c r="F20" t="n">
         <v>128.8896287080119</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>364.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>389.4520317029607</v>
+        <v>411.4478973282775</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>342.4496984536982</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2331,10 +2331,10 @@
         <v>127.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>132.0096587035274</v>
+        <v>132.2678500889416</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2581913854141848</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>9.53621805555548</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
@@ -2504,25 +2504,25 @@
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>244.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>295.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>364.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>389.4520317029607</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>106.7058584998675</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>86.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2540,7 +2540,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>11.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -2550,13 +2550,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0</v>
+        <v>238.5479778431551</v>
       </c>
       <c r="C26" t="n">
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>66.46383827095239</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
         <v>269.8481678023229</v>
       </c>
       <c r="T26" t="n">
-        <v>361.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
         <v>424.2212965486107</v>
@@ -2708,10 +2708,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>62.11380033707866</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>47.72524664804467</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -2723,10 +2723,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>20.04387284153003</v>
       </c>
       <c r="H28" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2735,7 +2735,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>63.52077380114304</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2750,10 +2750,10 @@
         <v>0</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>152.5170418010595</v>
       </c>
       <c r="Q28" t="n">
-        <v>340.7767994885276</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2808,16 +2808,16 @@
         <v>119.0096587035274</v>
       </c>
       <c r="I29" t="n">
-        <v>3.741391385414349</v>
+        <v>0</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>182.2760059786471</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>434.6628905091284</v>
+        <v>616.9388964877305</v>
       </c>
       <c r="M29" t="n">
         <v>0</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.74139138541444</v>
       </c>
       <c r="S29" t="n">
         <v>205.8481678023229</v>
@@ -2975,7 +2975,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>134.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>231.6316114025499</v>
@@ -2993,10 +2993,10 @@
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>187.390930659526</v>
+        <v>395.3120385201607</v>
       </c>
       <c r="S31" t="n">
-        <v>73.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3045,13 +3045,13 @@
         <v>119.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>3.741391385414349</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>616.9388964877456</v>
+        <v>182.2760059786919</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>434.662890509142</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>209.5895591877372</v>
+        <v>205.8481678023229</v>
       </c>
       <c r="T32" t="n">
         <v>297.6755817285639</v>
@@ -3218,16 +3218,16 @@
         <v>0</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>282.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>73.84156144051994</v>
+        <v>351.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>398.4478973282775</v>
+        <v>275.4980858436956</v>
       </c>
       <c r="Q34" t="n">
-        <v>436.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3288,10 +3288,10 @@
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>62.12488247690044</v>
+        <v>594.2484260902238</v>
       </c>
       <c r="L35" t="n">
-        <v>554.8140140107854</v>
+        <v>22.69047039753865</v>
       </c>
       <c r="M35" t="n">
         <v>0</v>
@@ -3458,16 +3458,16 @@
         <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>73.84156144051994</v>
       </c>
       <c r="P37" t="n">
-        <v>34.68733078764637</v>
+        <v>398.4478973282775</v>
       </c>
       <c r="Q37" t="n">
         <v>436.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>437.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3525,10 +3525,10 @@
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>62.12488247690044</v>
+        <v>0</v>
       </c>
       <c r="L38" t="n">
-        <v>554.5269539701297</v>
+        <v>616.6518364470983</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
@@ -3561,13 +3561,13 @@
         <v>340.8510241668239</v>
       </c>
       <c r="W38" t="n">
-        <v>353.114867366362</v>
+        <v>349.3734759809475</v>
       </c>
       <c r="X38" t="n">
         <v>303.2818334606677</v>
       </c>
       <c r="Y38" t="n">
-        <v>222.3174326828064</v>
+        <v>226.0588240682208</v>
       </c>
     </row>
     <row r="39">
@@ -3686,25 +3686,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>134.5476281577792</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>159.235263787103</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>351.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>398.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>336.9789690554652</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>437.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -3735,10 +3735,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>93.69578880096185</v>
+        <v>303.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>271.4745782429939</v>
       </c>
       <c r="D41" t="n">
         <v>0</v>
@@ -3747,13 +3747,13 @@
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>226.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>225.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>230.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3789,13 +3789,13 @@
         <v>316.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>408.6755817285639</v>
+        <v>29.40927648203205</v>
       </c>
       <c r="U41" t="n">
         <v>471.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>451.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
         <v>460.3734759809475</v>
@@ -3804,7 +3804,7 @@
         <v>414.2818334606677</v>
       </c>
       <c r="Y41" t="n">
-        <v>333.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -3817,10 +3817,10 @@
         <v>206.5565566463266</v>
       </c>
       <c r="C42" t="n">
-        <v>183.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>169.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>164.6720972219126</v>
@@ -3832,7 +3832,7 @@
         <v>147.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>154.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>39.12638589134853</v>
@@ -3862,19 +3862,19 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>35.3764001053413</v>
       </c>
       <c r="S42" t="n">
-        <v>0</v>
+        <v>288.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>227.3577652175138</v>
       </c>
       <c r="U42" t="n">
-        <v>222.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
-        <v>12.92331244885298</v>
+        <v>236.5106671915202</v>
       </c>
       <c r="W42" t="n">
         <v>254.3731429098285</v>
@@ -3883,7 +3883,7 @@
         <v>241.8627394453875</v>
       </c>
       <c r="Y42" t="n">
-        <v>221.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -3911,7 +3911,7 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>50.77112610161862</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -3941,13 +3941,13 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>84.93784149667631</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>32.02456650625771</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -3978,19 +3978,19 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>347.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>341.8896287080119</v>
       </c>
       <c r="G44" t="n">
-        <v>340.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>345.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4020,28 +4020,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>187.8785988282945</v>
       </c>
       <c r="S44" t="n">
-        <v>431.8481678023229</v>
+        <v>392.0215053320169</v>
       </c>
       <c r="T44" t="n">
-        <v>523.6755817285639</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>586.2212965486107</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>566.8510241668239</v>
       </c>
       <c r="W44" t="n">
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>167.1965181003389</v>
+        <v>529.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>448.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -4051,7 +4051,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0</v>
+        <v>321.5565566463266</v>
       </c>
       <c r="C45" t="n">
         <v>0</v>
@@ -4060,7 +4060,7 @@
         <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>233.9582922091361</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>269.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>154.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4096,19 +4096,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>110.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>484.2737972923793</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>144.2457603414419</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>337.2103597601867</v>
       </c>
       <c r="V45" t="n">
         <v>0</v>
@@ -4297,22 +4297,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>299.2473161322752</v>
+        <v>1511.368528253488</v>
       </c>
       <c r="C2" t="n">
-        <v>249.2729946747056</v>
+        <v>1461.394206795918</v>
       </c>
       <c r="D2" t="n">
-        <v>238.8294030182917</v>
+        <v>1046.9102110991</v>
       </c>
       <c r="E2" t="n">
-        <v>234.4220397790304</v>
+        <v>1042.502847859839</v>
       </c>
       <c r="F2" t="n">
-        <v>229.4830208820487</v>
+        <v>1037.563828962857</v>
       </c>
       <c r="G2" t="n">
-        <v>225.6876953396081</v>
+        <v>629.7280993800122</v>
       </c>
       <c r="H2" t="n">
         <v>217.5971309926107</v>
@@ -4321,52 +4321,52 @@
         <v>66</v>
       </c>
       <c r="J2" t="n">
-        <v>66</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="K2" t="n">
-        <v>775.7063663478683</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="L2" t="n">
-        <v>1592.456366347868</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="M2" t="n">
-        <v>2103.305195076804</v>
+        <v>614.6805851725693</v>
       </c>
       <c r="N2" t="n">
-        <v>2103.305195076804</v>
+        <v>1227.900904947332</v>
       </c>
       <c r="O2" t="n">
-        <v>2920.055195076804</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="P2" t="n">
-        <v>2920.055195076804</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q2" t="n">
         <v>3300</v>
       </c>
       <c r="R2" t="n">
-        <v>3300</v>
+        <v>3046.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>2814.115960095906</v>
+        <v>2950.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>2221.514362390286</v>
+        <v>2762.219850142241</v>
       </c>
       <c r="U2" t="n">
-        <v>1969.775679007851</v>
+        <v>2510.481166759806</v>
       </c>
       <c r="V2" t="n">
-        <v>1333.562523283787</v>
+        <v>2278.308415076146</v>
       </c>
       <c r="W2" t="n">
-        <v>1092.781234414143</v>
+        <v>1900.862042494951</v>
       </c>
       <c r="X2" t="n">
-        <v>898.5571602114479</v>
+        <v>1706.637968292256</v>
       </c>
       <c r="Y2" t="n">
-        <v>786.115309016694</v>
+        <v>1594.196117097502</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="C3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="D3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="E3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="G3" t="n">
-        <v>66</v>
+        <v>353.521575043377</v>
       </c>
       <c r="H3" t="n">
         <v>66</v>
@@ -4421,31 +4421,31 @@
         <v>1221.432420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1221.432420368536</v>
+        <v>1046.604879873102</v>
       </c>
       <c r="R3" t="n">
-        <v>1072.671008962092</v>
+        <v>897.8434684666579</v>
       </c>
       <c r="S3" t="n">
-        <v>1005.434645361474</v>
+        <v>830.6071048660405</v>
       </c>
       <c r="T3" t="n">
-        <v>1000.02276130338</v>
+        <v>825.1952208079457</v>
       </c>
       <c r="U3" t="n">
-        <v>595.7698726567262</v>
+        <v>824.9827362016964</v>
       </c>
       <c r="V3" t="n">
-        <v>581.1126330693321</v>
+        <v>406.2850925738982</v>
       </c>
       <c r="W3" t="n">
-        <v>548.41248871597</v>
+        <v>373.5849482205361</v>
       </c>
       <c r="X3" t="n">
-        <v>528.3491155388108</v>
+        <v>353.521575043377</v>
       </c>
       <c r="Y3" t="n">
-        <v>454.4409663094208</v>
+        <v>353.521575043377</v>
       </c>
     </row>
     <row r="4">
@@ -4455,31 +4455,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>772.3730652837567</v>
+        <v>461.0575566050018</v>
       </c>
       <c r="C4" t="n">
-        <v>898.3750711021925</v>
+        <v>587.0595624234376</v>
       </c>
       <c r="D4" t="n">
-        <v>1011.694215227193</v>
+        <v>700.3787065484377</v>
       </c>
       <c r="E4" t="n">
-        <v>1129.523119438606</v>
+        <v>818.2076107598507</v>
       </c>
       <c r="F4" t="n">
-        <v>1253.884092030541</v>
+        <v>942.5685833517862</v>
       </c>
       <c r="G4" t="n">
-        <v>1407.290657917426</v>
+        <v>1095.975149238672</v>
       </c>
       <c r="H4" t="n">
-        <v>1576.807243076824</v>
+        <v>1245.309930203873</v>
       </c>
       <c r="I4" t="n">
-        <v>1576.807243076824</v>
+        <v>1466.442809139956</v>
       </c>
       <c r="J4" t="n">
-        <v>1576.807243076824</v>
+        <v>1466.442809139956</v>
       </c>
       <c r="K4" t="n">
         <v>1576.807243076824</v>
@@ -4515,16 +4515,16 @@
         <v>66</v>
       </c>
       <c r="V4" t="n">
-        <v>226.2847176545613</v>
+        <v>66</v>
       </c>
       <c r="W4" t="n">
-        <v>398.1756359142387</v>
+        <v>237.8909182596774</v>
       </c>
       <c r="X4" t="n">
-        <v>549.2064269384322</v>
+        <v>237.8909182596774</v>
       </c>
       <c r="Y4" t="n">
-        <v>660.6157276174645</v>
+        <v>349.3002189387097</v>
       </c>
     </row>
     <row r="5">
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>551.6905891800685</v>
+        <v>703.2877201726793</v>
       </c>
       <c r="C5" t="n">
-        <v>501.7162677224989</v>
+        <v>653.3133987151097</v>
       </c>
       <c r="D5" t="n">
-        <v>491.272676066085</v>
+        <v>642.8698070586958</v>
       </c>
       <c r="E5" t="n">
-        <v>486.8653128268238</v>
+        <v>638.4624438194345</v>
       </c>
       <c r="F5" t="n">
-        <v>481.9262939298421</v>
+        <v>633.5234249224528</v>
       </c>
       <c r="G5" t="n">
-        <v>74.09056434699738</v>
+        <v>629.7280993800122</v>
       </c>
       <c r="H5" t="n">
-        <v>66</v>
+        <v>217.5971309926107</v>
       </c>
       <c r="I5" t="n">
         <v>66</v>
       </c>
       <c r="J5" t="n">
-        <v>66</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="K5" t="n">
-        <v>775.7063663478683</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="L5" t="n">
-        <v>1359.180851496302</v>
+        <v>457.3091130376557</v>
       </c>
       <c r="M5" t="n">
-        <v>1870.029680225237</v>
+        <v>614.6805851725693</v>
       </c>
       <c r="N5" t="n">
-        <v>2483.25</v>
+        <v>1227.900904947332</v>
       </c>
       <c r="O5" t="n">
-        <v>2483.25</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="P5" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q5" t="n">
         <v>3300</v>
@@ -4597,13 +4597,13 @@
         <v>1470.227606995337</v>
       </c>
       <c r="W5" t="n">
-        <v>1229.446318125693</v>
+        <v>1092.781234414143</v>
       </c>
       <c r="X5" t="n">
-        <v>1035.222243922999</v>
+        <v>898.5571602114479</v>
       </c>
       <c r="Y5" t="n">
-        <v>922.7803927282447</v>
+        <v>786.115309016694</v>
       </c>
     </row>
     <row r="6">
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>763.5856405248639</v>
+        <v>752.9755293779028</v>
       </c>
       <c r="C6" t="n">
-        <v>763.5856405248639</v>
+        <v>752.9755293779028</v>
       </c>
       <c r="D6" t="n">
-        <v>412.1334315372855</v>
+        <v>401.5233203903244</v>
       </c>
       <c r="E6" t="n">
-        <v>66</v>
+        <v>401.5233203903244</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>401.5233203903244</v>
       </c>
       <c r="G6" t="n">
-        <v>66</v>
+        <v>401.5233203903244</v>
       </c>
       <c r="H6" t="n">
         <v>66</v>
@@ -4667,22 +4667,22 @@
         <v>1005.434645361474</v>
       </c>
       <c r="T6" t="n">
-        <v>1000.02276130338</v>
+        <v>820.6087711020675</v>
       </c>
       <c r="U6" t="n">
-        <v>999.8102766971302</v>
+        <v>820.3962864958182</v>
       </c>
       <c r="V6" t="n">
-        <v>985.1530371097361</v>
+        <v>805.7390469084241</v>
       </c>
       <c r="W6" t="n">
-        <v>952.452892756374</v>
+        <v>773.038902555062</v>
       </c>
       <c r="X6" t="n">
-        <v>763.5856405248639</v>
+        <v>752.9755293779028</v>
       </c>
       <c r="Y6" t="n">
-        <v>763.5856405248639</v>
+        <v>752.9755293779028</v>
       </c>
     </row>
     <row r="7">
@@ -4692,31 +4692,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>922.6149030283618</v>
+        <v>772.3730652837567</v>
       </c>
       <c r="C7" t="n">
-        <v>1048.616908846798</v>
+        <v>898.3750711021925</v>
       </c>
       <c r="D7" t="n">
-        <v>1161.936052971798</v>
+        <v>1011.694215227193</v>
       </c>
       <c r="E7" t="n">
-        <v>1161.936052971798</v>
+        <v>1129.523119438606</v>
       </c>
       <c r="F7" t="n">
-        <v>1161.936052971798</v>
+        <v>1253.884092030541</v>
       </c>
       <c r="G7" t="n">
-        <v>1161.936052971798</v>
+        <v>1407.290657917426</v>
       </c>
       <c r="H7" t="n">
-        <v>1245.309930203873</v>
+        <v>1576.807243076824</v>
       </c>
       <c r="I7" t="n">
-        <v>1466.442809139956</v>
+        <v>1576.807243076824</v>
       </c>
       <c r="J7" t="n">
-        <v>1466.442809139956</v>
+        <v>1576.807243076824</v>
       </c>
       <c r="K7" t="n">
         <v>1576.807243076824</v>
@@ -4743,25 +4743,25 @@
         <v>66</v>
       </c>
       <c r="S7" t="n">
-        <v>66</v>
+        <v>103.2502550941731</v>
       </c>
       <c r="T7" t="n">
-        <v>254.0756791588049</v>
+        <v>291.325934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>500.6268717970915</v>
+        <v>488.7248093577871</v>
       </c>
       <c r="V7" t="n">
-        <v>699.4482646830375</v>
+        <v>488.7248093577871</v>
       </c>
       <c r="W7" t="n">
-        <v>699.4482646830375</v>
+        <v>660.6157276174645</v>
       </c>
       <c r="X7" t="n">
-        <v>699.4482646830375</v>
+        <v>660.6157276174645</v>
       </c>
       <c r="Y7" t="n">
-        <v>810.8575653620697</v>
+        <v>660.6157276174645</v>
       </c>
     </row>
     <row r="8">
@@ -4771,22 +4771,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1093.365529973416</v>
+        <v>1763.81180130128</v>
       </c>
       <c r="C8" t="n">
-        <v>1043.391208515846</v>
+        <v>1713.837479843711</v>
       </c>
       <c r="D8" t="n">
-        <v>1032.947616859432</v>
+        <v>1703.393888187297</v>
       </c>
       <c r="E8" t="n">
-        <v>890.9057168672277</v>
+        <v>1294.946120907632</v>
       </c>
       <c r="F8" t="n">
-        <v>481.9262939298421</v>
+        <v>885.9666979702461</v>
       </c>
       <c r="G8" t="n">
-        <v>74.09056434699738</v>
+        <v>478.1309683874014</v>
       </c>
       <c r="H8" t="n">
         <v>66</v>
@@ -4801,19 +4801,19 @@
         <v>1167.015479385524</v>
       </c>
       <c r="L8" t="n">
-        <v>1359.180851496302</v>
+        <v>1167.015479385524</v>
       </c>
       <c r="M8" t="n">
-        <v>1870.029680225237</v>
+        <v>1167.015479385524</v>
       </c>
       <c r="N8" t="n">
-        <v>2483.25</v>
+        <v>1227.900904947332</v>
       </c>
       <c r="O8" t="n">
-        <v>2483.25</v>
+        <v>2044.650904947332</v>
       </c>
       <c r="P8" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q8" t="n">
         <v>3300</v>
@@ -4822,25 +4822,25 @@
         <v>3300</v>
       </c>
       <c r="S8" t="n">
-        <v>2800.153365856239</v>
+        <v>3204.193769896644</v>
       </c>
       <c r="T8" t="n">
-        <v>2207.551768150619</v>
+        <v>2877.998039478483</v>
       </c>
       <c r="U8" t="n">
-        <v>1955.813084768184</v>
+        <v>2626.259356096048</v>
       </c>
       <c r="V8" t="n">
-        <v>1723.640333084523</v>
+        <v>2394.086604412388</v>
       </c>
       <c r="W8" t="n">
-        <v>1482.859044214879</v>
+        <v>2153.305315542744</v>
       </c>
       <c r="X8" t="n">
-        <v>1288.634970012185</v>
+        <v>1959.081241340049</v>
       </c>
       <c r="Y8" t="n">
-        <v>1176.193118817431</v>
+        <v>1846.639390145295</v>
       </c>
     </row>
     <row r="9">
@@ -4850,13 +4850,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>932.3895195792148</v>
+        <v>66</v>
       </c>
       <c r="C9" t="n">
-        <v>763.5856405248639</v>
+        <v>66</v>
       </c>
       <c r="D9" t="n">
-        <v>412.1334315372855</v>
+        <v>66</v>
       </c>
       <c r="E9" t="n">
         <v>66</v>
@@ -4910,16 +4910,16 @@
         <v>999.8102766971302</v>
       </c>
       <c r="V9" t="n">
-        <v>985.1530371097361</v>
+        <v>581.1126330693321</v>
       </c>
       <c r="W9" t="n">
-        <v>952.452892756374</v>
+        <v>144.3720846755659</v>
       </c>
       <c r="X9" t="n">
-        <v>932.3895195792148</v>
+        <v>66</v>
       </c>
       <c r="Y9" t="n">
-        <v>932.3895195792148</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10">
@@ -4929,31 +4929,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1057.460933153428</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="C10" t="n">
-        <v>1183.462938971864</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="D10" t="n">
-        <v>1296.782083096864</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="E10" t="n">
-        <v>1414.610987308277</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="F10" t="n">
-        <v>1538.971959900212</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="G10" t="n">
-        <v>1576.807243076824</v>
+        <v>714.7096043920239</v>
       </c>
       <c r="H10" t="n">
-        <v>1576.807243076824</v>
+        <v>884.2261895514215</v>
       </c>
       <c r="I10" t="n">
-        <v>1576.807243076824</v>
+        <v>1105.359068487504</v>
       </c>
       <c r="J10" t="n">
-        <v>1576.807243076824</v>
+        <v>1466.442809139956</v>
       </c>
       <c r="K10" t="n">
         <v>1576.807243076824</v>
@@ -4980,25 +4980,25 @@
         <v>66</v>
       </c>
       <c r="S10" t="n">
-        <v>66</v>
+        <v>103.2502550941731</v>
       </c>
       <c r="T10" t="n">
-        <v>66</v>
+        <v>103.2502550941731</v>
       </c>
       <c r="U10" t="n">
-        <v>312.5511926382866</v>
+        <v>349.8014477324598</v>
       </c>
       <c r="V10" t="n">
-        <v>511.3725855242326</v>
+        <v>349.8014477324598</v>
       </c>
       <c r="W10" t="n">
-        <v>683.26350378391</v>
+        <v>521.6923659921372</v>
       </c>
       <c r="X10" t="n">
-        <v>834.2942948081035</v>
+        <v>672.7231570163307</v>
       </c>
       <c r="Y10" t="n">
-        <v>945.7035954871358</v>
+        <v>672.7231570163307</v>
       </c>
     </row>
     <row r="11">
@@ -5008,19 +5008,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>845.9865477709493</v>
+        <v>1027.081205738787</v>
       </c>
       <c r="C11" t="n">
-        <v>619.244549545703</v>
+        <v>800.3392075135407</v>
       </c>
       <c r="D11" t="n">
-        <v>432.0332811216122</v>
+        <v>613.12793908945</v>
       </c>
       <c r="E11" t="n">
-        <v>250.8582411146742</v>
+        <v>613.12793908945</v>
       </c>
       <c r="F11" t="n">
-        <v>250.8582411146742</v>
+        <v>431.4212434247916</v>
       </c>
       <c r="G11" t="n">
         <v>250.8582411146742</v>
@@ -5032,25 +5032,25 @@
         <v>66</v>
       </c>
       <c r="J11" t="n">
-        <v>457.3091130376557</v>
+        <v>66</v>
       </c>
       <c r="K11" t="n">
-        <v>1167.015479385524</v>
+        <v>775.7063663478683</v>
       </c>
       <c r="L11" t="n">
-        <v>1983.765479385524</v>
+        <v>1592.456366347868</v>
       </c>
       <c r="M11" t="n">
-        <v>2483.25</v>
+        <v>2103.305195076804</v>
       </c>
       <c r="N11" t="n">
-        <v>2483.25</v>
+        <v>2716.525514851567</v>
       </c>
       <c r="O11" t="n">
-        <v>3300</v>
+        <v>2716.525514851567</v>
       </c>
       <c r="P11" t="n">
-        <v>3300</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q11" t="n">
         <v>3300</v>
@@ -5059,25 +5059,25 @@
         <v>3273.860001183541</v>
       </c>
       <c r="S11" t="n">
-        <v>3001.286094312508</v>
+        <v>3158.261946503606</v>
       </c>
       <c r="T11" t="n">
-        <v>2635.957223879615</v>
+        <v>2792.933076070713</v>
       </c>
       <c r="U11" t="n">
-        <v>2221.28073543373</v>
+        <v>2364.426715920602</v>
       </c>
       <c r="V11" t="n">
-        <v>1812.340306982392</v>
+        <v>2364.426715920602</v>
       </c>
       <c r="W11" t="n">
-        <v>1394.791341345071</v>
+        <v>1946.877750283281</v>
       </c>
       <c r="X11" t="n">
-        <v>1394.791341345071</v>
+        <v>1575.885999312909</v>
       </c>
       <c r="Y11" t="n">
-        <v>1105.581813382641</v>
+        <v>1286.676471350479</v>
       </c>
     </row>
     <row r="12">
@@ -5117,13 +5117,13 @@
         <v>824.6493362696824</v>
       </c>
       <c r="L12" t="n">
-        <v>1122.720378378698</v>
+        <v>1318.749797864883</v>
       </c>
       <c r="M12" t="n">
-        <v>1431.550920121557</v>
+        <v>1627.580339607742</v>
       </c>
       <c r="N12" t="n">
-        <v>1787.581204729126</v>
+        <v>1983.61062421531</v>
       </c>
       <c r="O12" t="n">
         <v>2249.373656412844</v>
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>179.6982646830375</v>
+        <v>179.1642331365846</v>
       </c>
       <c r="C13" t="n">
-        <v>179.6982646830375</v>
+        <v>130.9569132900749</v>
       </c>
       <c r="D13" t="n">
-        <v>179.6982646830375</v>
+        <v>69.80921828446326</v>
       </c>
       <c r="E13" t="n">
-        <v>179.6982646830375</v>
+        <v>69.80921828446326</v>
       </c>
       <c r="F13" t="n">
-        <v>179.6982646830375</v>
+        <v>69.80921828446326</v>
       </c>
       <c r="G13" t="n">
-        <v>179.6982646830375</v>
+        <v>69.80921828446326</v>
       </c>
       <c r="H13" t="n">
-        <v>179.6982646830375</v>
+        <v>66</v>
       </c>
       <c r="I13" t="n">
-        <v>227.5811436191204</v>
+        <v>113.8828789360829</v>
       </c>
       <c r="J13" t="n">
-        <v>415.4148842715717</v>
+        <v>301.7166195885342</v>
       </c>
       <c r="K13" t="n">
-        <v>415.4148842715717</v>
+        <v>301.7166195885342</v>
       </c>
       <c r="L13" t="n">
-        <v>415.4148842715717</v>
+        <v>101.1634598332017</v>
       </c>
       <c r="M13" t="n">
-        <v>415.4148842715717</v>
+        <v>101.1634598332017</v>
       </c>
       <c r="N13" t="n">
-        <v>415.4148842715717</v>
+        <v>101.1634598332017</v>
       </c>
       <c r="O13" t="n">
-        <v>415.4148842715717</v>
+        <v>66.85264505830446</v>
       </c>
       <c r="P13" t="n">
-        <v>66</v>
+        <v>66.85264505830446</v>
       </c>
       <c r="Q13" t="n">
-        <v>66</v>
+        <v>66.85264505830446</v>
       </c>
       <c r="R13" t="n">
-        <v>66</v>
+        <v>66.85264505830446</v>
       </c>
       <c r="S13" t="n">
-        <v>66</v>
+        <v>66.85264505830446</v>
       </c>
       <c r="T13" t="n">
-        <v>80.82567915880486</v>
+        <v>81.67832421710932</v>
       </c>
       <c r="U13" t="n">
-        <v>154.1268717970915</v>
+        <v>154.979516855396</v>
       </c>
       <c r="V13" t="n">
-        <v>179.6982646830375</v>
+        <v>180.5509097413419</v>
       </c>
       <c r="W13" t="n">
-        <v>179.6982646830375</v>
+        <v>179.1642331365846</v>
       </c>
       <c r="X13" t="n">
-        <v>179.6982646830375</v>
+        <v>179.1642331365846</v>
       </c>
       <c r="Y13" t="n">
-        <v>179.6982646830375</v>
+        <v>179.1642331365846</v>
       </c>
     </row>
     <row r="14">
@@ -5275,19 +5275,19 @@
         <v>1167.015479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1167.015479385524</v>
+        <v>1737.331756443634</v>
       </c>
       <c r="M14" t="n">
-        <v>1677.864308114459</v>
+        <v>2248.180585172569</v>
       </c>
       <c r="N14" t="n">
-        <v>2291.084627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="O14" t="n">
-        <v>3107.834627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="P14" t="n">
-        <v>3107.834627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q14" t="n">
         <v>3300</v>
@@ -5348,25 +5348,25 @@
         <v>66</v>
       </c>
       <c r="J15" t="n">
-        <v>189.9565201752989</v>
+        <v>285.3713555222668</v>
       </c>
       <c r="K15" t="n">
-        <v>379.1493362696824</v>
+        <v>747.8041716166501</v>
       </c>
       <c r="L15" t="n">
-        <v>650.4997978648825</v>
+        <v>1292.39463321185</v>
       </c>
       <c r="M15" t="n">
-        <v>1003.343647394284</v>
+        <v>1378.475174954709</v>
       </c>
       <c r="N15" t="n">
-        <v>1136.623932001853</v>
+        <v>1511.755459562278</v>
       </c>
       <c r="O15" t="n">
-        <v>1648.906383685571</v>
+        <v>1750.797911245997</v>
       </c>
       <c r="P15" t="n">
-        <v>1761.435728155078</v>
+        <v>1863.327255715503</v>
       </c>
       <c r="Q15" t="n">
         <v>1863.327255715503</v>
@@ -5430,28 +5430,28 @@
         <v>827.5127230120967</v>
       </c>
       <c r="K16" t="n">
-        <v>827.5127230120967</v>
+        <v>814.8654767483158</v>
       </c>
       <c r="L16" t="n">
-        <v>827.5127230120967</v>
+        <v>665.8274685081349</v>
       </c>
       <c r="M16" t="n">
-        <v>827.5127230120967</v>
+        <v>665.8274685081349</v>
       </c>
       <c r="N16" t="n">
-        <v>827.5127230120967</v>
+        <v>665.8274685081349</v>
       </c>
       <c r="O16" t="n">
-        <v>481.6039366952298</v>
+        <v>297.7006361050894</v>
       </c>
       <c r="P16" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="Q16" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="R16" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="S16" t="n">
         <v>66</v>
@@ -5482,22 +5482,22 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>899.4261360340223</v>
+        <v>899.1653366548161</v>
       </c>
       <c r="C17" t="n">
-        <v>724.1992893239275</v>
+        <v>723.9384899447213</v>
       </c>
       <c r="D17" t="n">
-        <v>588.5031724149883</v>
+        <v>588.2423730357821</v>
       </c>
       <c r="E17" t="n">
-        <v>458.8432839232017</v>
+        <v>458.5824845439955</v>
       </c>
       <c r="F17" t="n">
-        <v>328.6517397736948</v>
+        <v>328.3909403944886</v>
       </c>
       <c r="G17" t="n">
-        <v>199.6038889787289</v>
+        <v>199.3430895995226</v>
       </c>
       <c r="H17" t="n">
         <v>66</v>
@@ -5512,13 +5512,13 @@
         <v>1167.015479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1167.015479385524</v>
+        <v>1737.331756443634</v>
       </c>
       <c r="M17" t="n">
-        <v>1677.864308114459</v>
+        <v>2248.180585172569</v>
       </c>
       <c r="N17" t="n">
-        <v>2291.084627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="O17" t="n">
         <v>2861.400904947332</v>
@@ -5539,19 +5539,19 @@
         <v>2765.127525726377</v>
       </c>
       <c r="U17" t="n">
-        <v>2388.136317091416</v>
+        <v>2387.87551771221</v>
       </c>
       <c r="V17" t="n">
-        <v>2030.711040155231</v>
+        <v>2030.450240776024</v>
       </c>
       <c r="W17" t="n">
-        <v>1664.677226033061</v>
+        <v>1664.416426653855</v>
       </c>
       <c r="X17" t="n">
-        <v>1345.200626577841</v>
+        <v>1344.939827198635</v>
       </c>
       <c r="Y17" t="n">
-        <v>1107.506250130562</v>
+        <v>1107.245450751356</v>
       </c>
     </row>
     <row r="18">
@@ -5588,22 +5588,22 @@
         <v>248.2413981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>645.912644056225</v>
+        <v>437.4342142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>917.263105651425</v>
+        <v>708.7846758324474</v>
       </c>
       <c r="M18" t="n">
-        <v>1003.343647394284</v>
+        <v>1068.105217575307</v>
       </c>
       <c r="N18" t="n">
-        <v>1136.623932001853</v>
+        <v>1474.625502182875</v>
       </c>
       <c r="O18" t="n">
-        <v>1375.666383685571</v>
+        <v>1750.797911245997</v>
       </c>
       <c r="P18" t="n">
-        <v>1761.435728155078</v>
+        <v>1863.327255715503</v>
       </c>
       <c r="Q18" t="n">
         <v>1863.327255715503</v>
@@ -5676,13 +5676,13 @@
         <v>827.5127230120967</v>
       </c>
       <c r="N19" t="n">
-        <v>827.5127230120967</v>
+        <v>529.345980313425</v>
       </c>
       <c r="O19" t="n">
-        <v>827.5127230120967</v>
+        <v>529.345980313425</v>
       </c>
       <c r="P19" t="n">
-        <v>411.9087863168669</v>
+        <v>520.3830973995939</v>
       </c>
       <c r="Q19" t="n">
         <v>66</v>
@@ -5725,7 +5725,7 @@
         <v>724.1992893239275</v>
       </c>
       <c r="D20" t="n">
-        <v>588.2423730357821</v>
+        <v>588.5031724149883</v>
       </c>
       <c r="E20" t="n">
         <v>458.5824845439955</v>
@@ -5749,19 +5749,19 @@
         <v>775.7063663478683</v>
       </c>
       <c r="L20" t="n">
-        <v>1592.456366347868</v>
+        <v>1359.180851496298</v>
       </c>
       <c r="M20" t="n">
-        <v>2103.305195076804</v>
+        <v>1870.029680225233</v>
       </c>
       <c r="N20" t="n">
-        <v>2716.525514851567</v>
+        <v>2483.249999999996</v>
       </c>
       <c r="O20" t="n">
-        <v>2716.525514851567</v>
+        <v>2483.249999999996</v>
       </c>
       <c r="P20" t="n">
-        <v>2861.400904947332</v>
+        <v>3300</v>
       </c>
       <c r="Q20" t="n">
         <v>3300</v>
@@ -5819,28 +5819,28 @@
         <v>66</v>
       </c>
       <c r="I21" t="n">
-        <v>124.284877967565</v>
+        <v>66</v>
       </c>
       <c r="J21" t="n">
-        <v>248.2413981428639</v>
+        <v>189.9565201752989</v>
       </c>
       <c r="K21" t="n">
-        <v>645.9126440562247</v>
+        <v>379.1493362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>917.2631056514249</v>
+        <v>650.4997978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>1276.583647394284</v>
+        <v>831.9951749547093</v>
       </c>
       <c r="N21" t="n">
-        <v>1409.863932001852</v>
+        <v>965.2754595622777</v>
       </c>
       <c r="O21" t="n">
-        <v>1648.906383685571</v>
+        <v>1477.557911245997</v>
       </c>
       <c r="P21" t="n">
-        <v>1761.435728155078</v>
+        <v>1863.327255715503</v>
       </c>
       <c r="Q21" t="n">
         <v>1863.327255715503</v>
@@ -5916,13 +5916,13 @@
         <v>827.5127230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>459.3858906090512</v>
+        <v>827.5127230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>66</v>
+        <v>411.9087863168669</v>
       </c>
       <c r="Q22" t="n">
-        <v>66</v>
+        <v>411.9087863168669</v>
       </c>
       <c r="R22" t="n">
         <v>66</v>
@@ -5974,7 +5974,7 @@
         <v>199.6038889787289</v>
       </c>
       <c r="H23" t="n">
-        <v>66.26079937920625</v>
+        <v>66</v>
       </c>
       <c r="I23" t="n">
         <v>66</v>
@@ -5983,22 +5983,22 @@
         <v>457.3091130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1167.015479385524</v>
+        <v>614.6805851725616</v>
       </c>
       <c r="L23" t="n">
-        <v>1983.765479385524</v>
+        <v>614.6805851725616</v>
       </c>
       <c r="M23" t="n">
-        <v>2494.614308114459</v>
+        <v>614.6805851725616</v>
       </c>
       <c r="N23" t="n">
-        <v>3107.834627889222</v>
+        <v>1227.900904947325</v>
       </c>
       <c r="O23" t="n">
-        <v>3107.834627889222</v>
+        <v>2044.650904947329</v>
       </c>
       <c r="P23" t="n">
-        <v>3107.834627889222</v>
+        <v>2861.400904947332</v>
       </c>
       <c r="Q23" t="n">
         <v>3300</v>
@@ -6056,28 +6056,28 @@
         <v>66</v>
       </c>
       <c r="I24" t="n">
-        <v>124.284877967565</v>
+        <v>66</v>
       </c>
       <c r="J24" t="n">
-        <v>521.4813981428639</v>
+        <v>189.9565201752989</v>
       </c>
       <c r="K24" t="n">
-        <v>919.1526440562247</v>
+        <v>379.1493362696824</v>
       </c>
       <c r="L24" t="n">
-        <v>1190.503105651425</v>
+        <v>650.4997978648825</v>
       </c>
       <c r="M24" t="n">
-        <v>1276.583647394284</v>
+        <v>1009.820339607742</v>
       </c>
       <c r="N24" t="n">
-        <v>1409.863932001852</v>
+        <v>1416.34062421531</v>
       </c>
       <c r="O24" t="n">
-        <v>1648.906383685571</v>
+        <v>1655.383075899029</v>
       </c>
       <c r="P24" t="n">
-        <v>1761.435728155078</v>
+        <v>1767.912420368536</v>
       </c>
       <c r="Q24" t="n">
         <v>1863.327255715503</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>408.5699739669084</v>
+        <v>396.9888094725019</v>
       </c>
       <c r="C25" t="n">
-        <v>411.8119797853441</v>
+        <v>400.2308152909377</v>
       </c>
       <c r="D25" t="n">
-        <v>411.8119797853441</v>
+        <v>390.5982718004776</v>
       </c>
       <c r="E25" t="n">
-        <v>411.8119797853441</v>
+        <v>390.5982718004776</v>
       </c>
       <c r="F25" t="n">
-        <v>413.4129523772796</v>
+        <v>392.1992443924131</v>
       </c>
       <c r="G25" t="n">
-        <v>444.0595182641649</v>
+        <v>422.8458102792983</v>
       </c>
       <c r="H25" t="n">
-        <v>490.8161034235625</v>
+        <v>469.6023954386959</v>
       </c>
       <c r="I25" t="n">
-        <v>589.1889823596454</v>
+        <v>567.9752743747788</v>
       </c>
       <c r="J25" t="n">
-        <v>827.5127230120967</v>
+        <v>806.2990150272301</v>
       </c>
       <c r="K25" t="n">
-        <v>827.5127230120967</v>
+        <v>806.2990150272301</v>
       </c>
       <c r="L25" t="n">
-        <v>827.5127230120967</v>
+        <v>806.2990150272301</v>
       </c>
       <c r="M25" t="n">
-        <v>827.5127230120967</v>
+        <v>559.1963772468766</v>
       </c>
       <c r="N25" t="n">
-        <v>827.5127230120967</v>
+        <v>261.029634548205</v>
       </c>
       <c r="O25" t="n">
-        <v>459.3858906090512</v>
+        <v>261.029634548205</v>
       </c>
       <c r="P25" t="n">
-        <v>66</v>
+        <v>261.029634548205</v>
       </c>
       <c r="Q25" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="R25" t="n">
-        <v>66</v>
+        <v>153.2459390937934</v>
       </c>
       <c r="S25" t="n">
         <v>66</v>
@@ -6183,7 +6183,7 @@
         <v>408.5699739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>408.5699739669084</v>
+        <v>396.9888094725019</v>
       </c>
     </row>
     <row r="26">
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>536.760190708043</v>
+        <v>661.1315077640113</v>
       </c>
       <c r="C26" t="n">
-        <v>310.0181924827966</v>
+        <v>434.3895095387649</v>
       </c>
       <c r="D26" t="n">
-        <v>310.0181924827966</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="E26" t="n">
-        <v>310.0181924827966</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="F26" t="n">
-        <v>310.0181924827966</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="G26" t="n">
-        <v>129.4551901726792</v>
+        <v>247.1782411146742</v>
       </c>
       <c r="H26" t="n">
         <v>62.32</v>
@@ -6220,22 +6220,22 @@
         <v>62.32</v>
       </c>
       <c r="K26" t="n">
-        <v>62.32</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L26" t="n">
-        <v>449.5108514962735</v>
+        <v>1543.236366347868</v>
       </c>
       <c r="M26" t="n">
-        <v>960.3596802252085</v>
+        <v>2054.085195076803</v>
       </c>
       <c r="N26" t="n">
-        <v>1573.579999999972</v>
+        <v>2667.305514851566</v>
       </c>
       <c r="O26" t="n">
-        <v>2344.789999999986</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P26" t="n">
-        <v>3116</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="Q26" t="n">
         <v>3116</v>
@@ -6247,22 +6247,22 @@
         <v>2817.286094312508</v>
       </c>
       <c r="T26" t="n">
-        <v>2451.957223879615</v>
+        <v>2817.286094312508</v>
       </c>
       <c r="U26" t="n">
-        <v>2023.450863729503</v>
+        <v>2388.779734162396</v>
       </c>
       <c r="V26" t="n">
-        <v>1614.510435278166</v>
+        <v>1979.839305711059</v>
       </c>
       <c r="W26" t="n">
-        <v>1196.961469640845</v>
+        <v>1562.290340073738</v>
       </c>
       <c r="X26" t="n">
-        <v>825.9697186704736</v>
+        <v>1191.298589103366</v>
       </c>
       <c r="Y26" t="n">
-        <v>536.760190708043</v>
+        <v>902.0890611409357</v>
       </c>
     </row>
     <row r="27">
@@ -6302,7 +6302,7 @@
         <v>828.7642142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1322.864675832448</v>
+        <v>1119.040378378698</v>
       </c>
       <c r="M27" t="n">
         <v>1427.870920121557</v>
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>174.6315880782802</v>
+        <v>130.7736560500755</v>
       </c>
       <c r="C28" t="n">
-        <v>174.6315880782802</v>
+        <v>82.5663362035657</v>
       </c>
       <c r="D28" t="n">
-        <v>174.6315880782802</v>
+        <v>82.5663362035657</v>
       </c>
       <c r="E28" t="n">
-        <v>174.6315880782802</v>
+        <v>82.5663362035657</v>
       </c>
       <c r="F28" t="n">
-        <v>174.6315880782802</v>
+        <v>82.5663362035657</v>
       </c>
       <c r="G28" t="n">
-        <v>174.6315880782802</v>
+        <v>62.32</v>
       </c>
       <c r="H28" t="n">
-        <v>170.8223697938169</v>
+        <v>62.32</v>
       </c>
       <c r="I28" t="n">
-        <v>218.7052487298998</v>
+        <v>110.2028789360829</v>
       </c>
       <c r="J28" t="n">
-        <v>406.5389893823511</v>
+        <v>298.0366195885342</v>
       </c>
       <c r="K28" t="n">
-        <v>406.5389893823511</v>
+        <v>233.8742218096019</v>
       </c>
       <c r="L28" t="n">
-        <v>406.5389893823511</v>
+        <v>233.8742218096019</v>
       </c>
       <c r="M28" t="n">
-        <v>406.5389893823511</v>
+        <v>233.8742218096019</v>
       </c>
       <c r="N28" t="n">
-        <v>406.5389893823511</v>
+        <v>233.8742218096019</v>
       </c>
       <c r="O28" t="n">
-        <v>406.5389893823511</v>
+        <v>233.8742218096019</v>
       </c>
       <c r="P28" t="n">
-        <v>406.5389893823511</v>
+        <v>79.81660382873366</v>
       </c>
       <c r="Q28" t="n">
-        <v>62.32</v>
+        <v>79.81660382873366</v>
       </c>
       <c r="R28" t="n">
-        <v>62.32</v>
+        <v>79.81660382873366</v>
       </c>
       <c r="S28" t="n">
-        <v>62.32</v>
+        <v>79.81660382873366</v>
       </c>
       <c r="T28" t="n">
-        <v>77.14567915880487</v>
+        <v>94.64228298753852</v>
       </c>
       <c r="U28" t="n">
-        <v>150.4468717970915</v>
+        <v>167.9434756258252</v>
       </c>
       <c r="V28" t="n">
-        <v>176.0182646830374</v>
+        <v>193.5148685117711</v>
       </c>
       <c r="W28" t="n">
-        <v>174.6315880782802</v>
+        <v>193.5148685117711</v>
       </c>
       <c r="X28" t="n">
-        <v>174.6315880782802</v>
+        <v>193.5148685117711</v>
       </c>
       <c r="Y28" t="n">
-        <v>174.6315880782802</v>
+        <v>193.5148685117711</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>820.4766410845275</v>
+        <v>816.6974578669373</v>
       </c>
       <c r="C29" t="n">
-        <v>658.3811075057457</v>
+        <v>654.6019242881555</v>
       </c>
       <c r="D29" t="n">
-        <v>535.8163037281197</v>
+        <v>532.0371205105295</v>
       </c>
       <c r="E29" t="n">
-        <v>419.2877283676463</v>
+        <v>415.5085451500561</v>
       </c>
       <c r="F29" t="n">
-        <v>302.2274973494525</v>
+        <v>298.4483141318623</v>
       </c>
       <c r="G29" t="n">
-        <v>186.3109596857998</v>
+        <v>182.5317764682095</v>
       </c>
       <c r="H29" t="n">
-        <v>66.09918321759025</v>
+        <v>62.32</v>
       </c>
       <c r="I29" t="n">
         <v>62.32</v>
       </c>
       <c r="J29" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K29" t="n">
-        <v>449.9651812003071</v>
+        <v>74.72109499000599</v>
       </c>
       <c r="L29" t="n">
-        <v>782.1217564436116</v>
+        <v>62.32</v>
       </c>
       <c r="M29" t="n">
-        <v>1292.970585172547</v>
+        <v>573.1688287289351</v>
       </c>
       <c r="N29" t="n">
-        <v>1906.19090494731</v>
+        <v>1186.389148503698</v>
       </c>
       <c r="O29" t="n">
-        <v>1906.19090494731</v>
+        <v>1957.599148503714</v>
       </c>
       <c r="P29" t="n">
-        <v>2677.400904947332</v>
+        <v>2728.809148503729</v>
       </c>
       <c r="Q29" t="n">
         <v>3116</v>
       </c>
       <c r="R29" t="n">
-        <v>3116</v>
+        <v>3112.22081678241</v>
       </c>
       <c r="S29" t="n">
-        <v>2908.072557775432</v>
+        <v>2904.293374557841</v>
       </c>
       <c r="T29" t="n">
-        <v>2607.390151989003</v>
+        <v>2603.610968771413</v>
       </c>
       <c r="U29" t="n">
-        <v>2243.530256485356</v>
+        <v>2239.751073267766</v>
       </c>
       <c r="V29" t="n">
-        <v>1899.236292680483</v>
+        <v>1895.457109462893</v>
       </c>
       <c r="W29" t="n">
-        <v>1546.333791689627</v>
+        <v>1542.554608472037</v>
       </c>
       <c r="X29" t="n">
-        <v>1239.98850536572</v>
+        <v>1236.20932214813</v>
       </c>
       <c r="Y29" t="n">
-        <v>1015.425442049754</v>
+        <v>1011.646258832164</v>
       </c>
     </row>
     <row r="30">
@@ -6530,28 +6530,28 @@
         <v>62.32</v>
       </c>
       <c r="I30" t="n">
-        <v>106.3736108168454</v>
+        <v>133.474877967565</v>
       </c>
       <c r="J30" t="n">
-        <v>230.3301309921443</v>
+        <v>257.4313981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>419.5229470865277</v>
+        <v>446.6242142372473</v>
       </c>
       <c r="L30" t="n">
-        <v>690.8734086817278</v>
+        <v>1004.084675832447</v>
       </c>
       <c r="M30" t="n">
-        <v>776.9539504245871</v>
+        <v>1090.165217575307</v>
       </c>
       <c r="N30" t="n">
-        <v>910.2342350321554</v>
+        <v>1223.445502182875</v>
       </c>
       <c r="O30" t="n">
-        <v>1149.276686715874</v>
+        <v>1462.487953866594</v>
       </c>
       <c r="P30" t="n">
-        <v>1547.916031185381</v>
+        <v>1662.677558745806</v>
       </c>
       <c r="Q30" t="n">
         <v>1662.677558745806</v>
@@ -6618,25 +6618,25 @@
         <v>980.6318436307025</v>
       </c>
       <c r="L31" t="n">
-        <v>844.7251485218346</v>
+        <v>980.6318436307025</v>
       </c>
       <c r="M31" t="n">
-        <v>610.7538238727943</v>
+        <v>746.6605189816622</v>
       </c>
       <c r="N31" t="n">
-        <v>325.7183943054358</v>
+        <v>461.6250894143037</v>
       </c>
       <c r="O31" t="n">
-        <v>325.7183943054358</v>
+        <v>461.6250894143037</v>
       </c>
       <c r="P31" t="n">
-        <v>325.7183943054358</v>
+        <v>461.6250894143037</v>
       </c>
       <c r="Q31" t="n">
-        <v>325.7183943054358</v>
+        <v>461.6250894143037</v>
       </c>
       <c r="R31" t="n">
-        <v>136.4346259624803</v>
+        <v>62.32</v>
       </c>
       <c r="S31" t="n">
         <v>62.32</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>816.6974578669373</v>
+        <v>820.4766410845275</v>
       </c>
       <c r="C32" t="n">
-        <v>654.6019242881555</v>
+        <v>658.3811075057457</v>
       </c>
       <c r="D32" t="n">
-        <v>532.0371205105295</v>
+        <v>535.8163037281197</v>
       </c>
       <c r="E32" t="n">
-        <v>415.5085451500561</v>
+        <v>419.2877283676463</v>
       </c>
       <c r="F32" t="n">
-        <v>298.4483141318623</v>
+        <v>302.2274973494525</v>
       </c>
       <c r="G32" t="n">
-        <v>182.5317764682095</v>
+        <v>186.3109596857998</v>
       </c>
       <c r="H32" t="n">
-        <v>62.32</v>
+        <v>66.09918321759025</v>
       </c>
       <c r="I32" t="n">
         <v>62.32</v>
@@ -6694,19 +6694,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K32" t="n">
-        <v>441.2280180476494</v>
+        <v>449.9651812003062</v>
       </c>
       <c r="L32" t="n">
-        <v>1212.438018047649</v>
+        <v>449.9651812003062</v>
       </c>
       <c r="M32" t="n">
-        <v>1292.970585172543</v>
+        <v>960.8140099292413</v>
       </c>
       <c r="N32" t="n">
-        <v>1906.190904947307</v>
+        <v>1574.034329704004</v>
       </c>
       <c r="O32" t="n">
-        <v>1906.190904947307</v>
+        <v>2345.244329704023</v>
       </c>
       <c r="P32" t="n">
         <v>2677.400904947332</v>
@@ -6718,25 +6718,25 @@
         <v>3116</v>
       </c>
       <c r="S32" t="n">
-        <v>2904.293374557841</v>
+        <v>2908.072557775432</v>
       </c>
       <c r="T32" t="n">
-        <v>2603.610968771413</v>
+        <v>2607.390151989003</v>
       </c>
       <c r="U32" t="n">
-        <v>2239.751073267766</v>
+        <v>2243.530256485356</v>
       </c>
       <c r="V32" t="n">
-        <v>1895.457109462893</v>
+        <v>1899.236292680483</v>
       </c>
       <c r="W32" t="n">
-        <v>1542.554608472037</v>
+        <v>1546.333791689627</v>
       </c>
       <c r="X32" t="n">
-        <v>1236.20932214813</v>
+        <v>1239.98850536572</v>
       </c>
       <c r="Y32" t="n">
-        <v>1011.646258832164</v>
+        <v>1015.425442049754</v>
       </c>
     </row>
     <row r="33">
@@ -6767,25 +6767,25 @@
         <v>62.32</v>
       </c>
       <c r="I33" t="n">
-        <v>106.3736108168454</v>
+        <v>133.474877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>230.3301309921443</v>
+        <v>257.4313981428639</v>
       </c>
       <c r="K33" t="n">
-        <v>419.5229470865277</v>
+        <v>446.6242142372473</v>
       </c>
       <c r="L33" t="n">
-        <v>690.8734086817278</v>
+        <v>717.9746758324475</v>
       </c>
       <c r="M33" t="n">
-        <v>776.9539504245871</v>
+        <v>1063.063950424587</v>
       </c>
       <c r="N33" t="n">
-        <v>910.2342350321554</v>
+        <v>1196.344235032156</v>
       </c>
       <c r="O33" t="n">
-        <v>1149.276686715874</v>
+        <v>1435.386686715874</v>
       </c>
       <c r="P33" t="n">
         <v>1547.916031185381</v>
@@ -6861,13 +6861,13 @@
         <v>980.6318436307025</v>
       </c>
       <c r="N34" t="n">
-        <v>980.6318436307025</v>
+        <v>695.596414063344</v>
       </c>
       <c r="O34" t="n">
-        <v>906.0444078321975</v>
+        <v>340.6008947916117</v>
       </c>
       <c r="P34" t="n">
-        <v>503.5717842682809</v>
+        <v>62.32</v>
       </c>
       <c r="Q34" t="n">
         <v>62.32</v>
@@ -6931,19 +6931,19 @@
         <v>453.6291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>1162.086706495332</v>
+        <v>624.5881775929849</v>
       </c>
       <c r="L35" t="n">
-        <v>1372.878510524842</v>
+        <v>624.1320762183274</v>
       </c>
       <c r="M35" t="n">
-        <v>1883.727339253777</v>
+        <v>1134.980904947262</v>
       </c>
       <c r="N35" t="n">
-        <v>2496.94765902854</v>
+        <v>1134.980904947262</v>
       </c>
       <c r="O35" t="n">
-        <v>2677.400904947332</v>
+        <v>1906.190904947297</v>
       </c>
       <c r="P35" t="n">
         <v>2677.400904947332</v>
@@ -7004,28 +7004,28 @@
         <v>62.32</v>
       </c>
       <c r="I36" t="n">
-        <v>133.474877967565</v>
+        <v>62.32</v>
       </c>
       <c r="J36" t="n">
-        <v>257.4313981428639</v>
+        <v>345.0916585525698</v>
       </c>
       <c r="K36" t="n">
-        <v>446.6242142372473</v>
+        <v>534.2844746469532</v>
       </c>
       <c r="L36" t="n">
-        <v>717.9746758324475</v>
+        <v>805.6349362421532</v>
       </c>
       <c r="M36" t="n">
-        <v>804.0552175753068</v>
+        <v>891.7154779850125</v>
       </c>
       <c r="N36" t="n">
-        <v>1196.344235032156</v>
+        <v>1024.995762592581</v>
       </c>
       <c r="O36" t="n">
-        <v>1435.386686715874</v>
+        <v>1550.1482142763</v>
       </c>
       <c r="P36" t="n">
-        <v>1547.916031185381</v>
+        <v>1662.677558745806</v>
       </c>
       <c r="Q36" t="n">
         <v>1662.677558745806</v>
@@ -7101,13 +7101,13 @@
         <v>980.6318436307025</v>
       </c>
       <c r="O37" t="n">
-        <v>980.6318436307025</v>
+        <v>906.0444078321975</v>
       </c>
       <c r="P37" t="n">
-        <v>945.5941357643931</v>
+        <v>503.5717842682809</v>
       </c>
       <c r="Q37" t="n">
-        <v>504.3423514961122</v>
+        <v>62.32</v>
       </c>
       <c r="R37" t="n">
         <v>62.32</v>
@@ -7165,19 +7165,19 @@
         <v>62.32</v>
       </c>
       <c r="J38" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K38" t="n">
-        <v>1162.086706495332</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L38" t="n">
-        <v>1150.940154592296</v>
+        <v>920.3557234720113</v>
       </c>
       <c r="M38" t="n">
-        <v>1661.788983321231</v>
+        <v>1431.204552200946</v>
       </c>
       <c r="N38" t="n">
-        <v>2275.009303095994</v>
+        <v>2044.424871975709</v>
       </c>
       <c r="O38" t="n">
         <v>2677.690864584385</v>
@@ -7204,10 +7204,10 @@
         <v>1899.236292680483</v>
       </c>
       <c r="W38" t="n">
-        <v>1542.554608472037</v>
+        <v>1546.333791689627</v>
       </c>
       <c r="X38" t="n">
-        <v>1236.20932214813</v>
+        <v>1239.98850536572</v>
       </c>
       <c r="Y38" t="n">
         <v>1011.646258832164</v>
@@ -7241,28 +7241,28 @@
         <v>62.32</v>
       </c>
       <c r="I39" t="n">
-        <v>133.474877967565</v>
+        <v>62.32</v>
       </c>
       <c r="J39" t="n">
-        <v>257.4313981428639</v>
+        <v>186.2765201752989</v>
       </c>
       <c r="K39" t="n">
-        <v>705.632947086528</v>
+        <v>661.5793362696824</v>
       </c>
       <c r="L39" t="n">
-        <v>976.9834086817281</v>
+        <v>1091.744936242153</v>
       </c>
       <c r="M39" t="n">
-        <v>1063.063950424587</v>
+        <v>1177.825477985013</v>
       </c>
       <c r="N39" t="n">
-        <v>1196.344235032156</v>
+        <v>1311.105762592581</v>
       </c>
       <c r="O39" t="n">
-        <v>1435.386686715874</v>
+        <v>1550.1482142763</v>
       </c>
       <c r="P39" t="n">
-        <v>1547.916031185381</v>
+        <v>1662.677558745806</v>
       </c>
       <c r="Q39" t="n">
         <v>1662.677558745806</v>
@@ -7329,22 +7329,22 @@
         <v>980.6318436307025</v>
       </c>
       <c r="L40" t="n">
-        <v>980.6318436307025</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="M40" t="n">
-        <v>980.6318436307025</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="N40" t="n">
-        <v>819.788142835649</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="O40" t="n">
-        <v>464.7926235639167</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="P40" t="n">
-        <v>62.32</v>
+        <v>844.7251485218346</v>
       </c>
       <c r="Q40" t="n">
-        <v>62.32</v>
+        <v>504.3423514961122</v>
       </c>
       <c r="R40" t="n">
         <v>62.32</v>
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>62.32</v>
+        <v>1026.088927213686</v>
       </c>
       <c r="C41" t="n">
-        <v>62.32</v>
+        <v>751.8721815136925</v>
       </c>
       <c r="D41" t="n">
-        <v>62.32</v>
+        <v>751.8721815136925</v>
       </c>
       <c r="E41" t="n">
-        <v>62.32</v>
+        <v>751.8721815136925</v>
       </c>
       <c r="F41" t="n">
-        <v>62.32</v>
+        <v>522.6907383742865</v>
       </c>
       <c r="G41" t="n">
-        <v>62.32</v>
+        <v>294.6529885894216</v>
       </c>
       <c r="H41" t="n">
         <v>62.32</v>
@@ -7402,22 +7402,22 @@
         <v>62.32</v>
       </c>
       <c r="J41" t="n">
-        <v>62.32</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="K41" t="n">
-        <v>772.0263663478684</v>
+        <v>453.6291130376557</v>
       </c>
       <c r="L41" t="n">
-        <v>1395.342076218304</v>
+        <v>782.1217564435552</v>
       </c>
       <c r="M41" t="n">
-        <v>1906.190904947239</v>
+        <v>1292.97058517249</v>
       </c>
       <c r="N41" t="n">
-        <v>1906.190904947239</v>
+        <v>1906.190904947253</v>
       </c>
       <c r="O41" t="n">
-        <v>1906.190904947239</v>
+        <v>2677.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2677.400904947332</v>
@@ -7432,22 +7432,22 @@
         <v>2722.336599363012</v>
       </c>
       <c r="T41" t="n">
-        <v>2309.532981455372</v>
+        <v>2692.630259482172</v>
       </c>
       <c r="U41" t="n">
-        <v>1833.551873830513</v>
+        <v>2216.649151857313</v>
       </c>
       <c r="V41" t="n">
-        <v>1377.136697904428</v>
+        <v>2216.649151857313</v>
       </c>
       <c r="W41" t="n">
-        <v>912.1129847923596</v>
+        <v>1751.625438745244</v>
       </c>
       <c r="X41" t="n">
-        <v>493.6464863472407</v>
+        <v>1333.158940300125</v>
       </c>
       <c r="Y41" t="n">
-        <v>156.9622109100625</v>
+        <v>1333.158940300125</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>937.2814754236235</v>
+        <v>736.403180315744</v>
       </c>
       <c r="C42" t="n">
-        <v>752.332068912998</v>
+        <v>736.403180315744</v>
       </c>
       <c r="D42" t="n">
-        <v>580.6778397233994</v>
+        <v>736.403180315744</v>
       </c>
       <c r="E42" t="n">
-        <v>414.3423879840938</v>
+        <v>570.0677285764383</v>
       </c>
       <c r="F42" t="n">
-        <v>251.0734563296726</v>
+        <v>406.7987969220172</v>
       </c>
       <c r="G42" t="n">
-        <v>101.8416019104531</v>
+        <v>257.5669425027976</v>
       </c>
       <c r="H42" t="n">
         <v>101.8416019104531</v>
@@ -7484,49 +7484,49 @@
         <v>362.4965201752989</v>
       </c>
       <c r="K42" t="n">
-        <v>727.9093362696824</v>
+        <v>690.0264186367984</v>
       </c>
       <c r="L42" t="n">
-        <v>1175.479797864883</v>
+        <v>1137.596880231999</v>
       </c>
       <c r="M42" t="n">
-        <v>1319.579957197587</v>
+        <v>1399.897421974858</v>
       </c>
       <c r="N42" t="n">
-        <v>1629.080241805155</v>
+        <v>1709.397706582426</v>
       </c>
       <c r="O42" t="n">
-        <v>2044.342693488874</v>
+        <v>1948.440158266145</v>
       </c>
       <c r="P42" t="n">
-        <v>2333.09203795838</v>
+        <v>2237.189502735651</v>
       </c>
       <c r="Q42" t="n">
-        <v>2337.963565518806</v>
+        <v>2242.061030296077</v>
       </c>
       <c r="R42" t="n">
-        <v>2337.963565518806</v>
+        <v>2206.327292815934</v>
       </c>
       <c r="S42" t="n">
-        <v>2337.963565518806</v>
+        <v>1914.848504972892</v>
       </c>
       <c r="T42" t="n">
-        <v>2108.309257218287</v>
+        <v>1685.194196672373</v>
       </c>
       <c r="U42" t="n">
-        <v>1883.854348369613</v>
+        <v>1685.194196672373</v>
       </c>
       <c r="V42" t="n">
-        <v>1870.800497411176</v>
+        <v>1446.294532842555</v>
       </c>
       <c r="W42" t="n">
-        <v>1613.85792881539</v>
+        <v>1189.351964246768</v>
       </c>
       <c r="X42" t="n">
-        <v>1369.552131395806</v>
+        <v>945.0461668271849</v>
       </c>
       <c r="Y42" t="n">
-        <v>1145.924461935065</v>
+        <v>945.0461668271849</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="C43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="D43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="E43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="F43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="G43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="H43" t="n">
         <v>62.32</v>
       </c>
       <c r="I43" t="n">
-        <v>62.32</v>
+        <v>63.67287893608291</v>
       </c>
       <c r="J43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="K43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="L43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="M43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="N43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="O43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="P43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="Q43" t="n">
-        <v>62.32</v>
+        <v>204.9766195885342</v>
       </c>
       <c r="R43" t="n">
-        <v>62.32</v>
+        <v>119.180820096942</v>
       </c>
       <c r="S43" t="n">
-        <v>62.32</v>
+        <v>119.180820096942</v>
       </c>
       <c r="T43" t="n">
-        <v>62.32</v>
+        <v>86.83277312092409</v>
       </c>
       <c r="U43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="V43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="W43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="X43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
       <c r="Y43" t="n">
-        <v>62.32</v>
+        <v>113.6039657592107</v>
       </c>
     </row>
     <row r="44">
@@ -7615,22 +7615,22 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1105.861602757973</v>
+        <v>407.6630593010221</v>
       </c>
       <c r="C44" t="n">
-        <v>1105.861602757973</v>
+        <v>407.6630593010221</v>
       </c>
       <c r="D44" t="n">
-        <v>755.0139706975189</v>
+        <v>407.6630593010221</v>
       </c>
       <c r="E44" t="n">
-        <v>755.0139706975189</v>
+        <v>407.6630593010221</v>
       </c>
       <c r="F44" t="n">
-        <v>755.0139706975189</v>
+        <v>62.32</v>
       </c>
       <c r="G44" t="n">
-        <v>410.8146047510378</v>
+        <v>62.32</v>
       </c>
       <c r="H44" t="n">
         <v>62.32</v>
@@ -7639,19 +7639,19 @@
         <v>62.32</v>
       </c>
       <c r="J44" t="n">
-        <v>453.6291130376557</v>
+        <v>62.32</v>
       </c>
       <c r="K44" t="n">
-        <v>782.1217564435075</v>
+        <v>772.0263663478684</v>
       </c>
       <c r="L44" t="n">
-        <v>782.1217564435075</v>
+        <v>1292.970585172457</v>
       </c>
       <c r="M44" t="n">
-        <v>1292.970585172442</v>
+        <v>1292.970585172457</v>
       </c>
       <c r="N44" t="n">
-        <v>1906.190904947206</v>
+        <v>1906.19090494722</v>
       </c>
       <c r="O44" t="n">
         <v>2677.400904947332</v>
@@ -7663,28 +7663,28 @@
         <v>3116</v>
       </c>
       <c r="R44" t="n">
-        <v>3116</v>
+        <v>2926.223637547178</v>
       </c>
       <c r="S44" t="n">
-        <v>2679.789729492603</v>
+        <v>2530.242319029989</v>
       </c>
       <c r="T44" t="n">
-        <v>2150.824495423347</v>
+        <v>2530.242319029989</v>
       </c>
       <c r="U44" t="n">
-        <v>2150.824495423347</v>
+        <v>1938.099595243513</v>
       </c>
       <c r="V44" t="n">
-        <v>2150.824495423347</v>
+        <v>1365.522803155812</v>
       </c>
       <c r="W44" t="n">
-        <v>2150.824495423347</v>
+        <v>1365.522803155812</v>
       </c>
       <c r="X44" t="n">
-        <v>1981.939123604823</v>
+        <v>830.8946885490772</v>
       </c>
       <c r="Y44" t="n">
-        <v>1529.093232006028</v>
+        <v>830.8946885490772</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>489.89017482603</v>
+        <v>570.5284640359164</v>
       </c>
       <c r="C45" t="n">
-        <v>489.89017482603</v>
+        <v>570.5284640359164</v>
       </c>
       <c r="D45" t="n">
-        <v>489.89017482603</v>
+        <v>570.5284640359164</v>
       </c>
       <c r="E45" t="n">
-        <v>489.89017482603</v>
+        <v>334.2069567539608</v>
       </c>
       <c r="F45" t="n">
-        <v>489.89017482603</v>
+        <v>334.2069567539608</v>
       </c>
       <c r="G45" t="n">
-        <v>489.89017482603</v>
+        <v>334.2069567539608</v>
       </c>
       <c r="H45" t="n">
-        <v>218.0032180720692</v>
+        <v>62.32</v>
       </c>
       <c r="I45" t="n">
         <v>62.32</v>
@@ -7721,7 +7721,7 @@
         <v>248.6465201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>500.2093362696824</v>
+        <v>437.8393362696823</v>
       </c>
       <c r="L45" t="n">
         <v>771.5597978648825</v>
@@ -7739,31 +7739,31 @@
         <v>1575.738877341621</v>
       </c>
       <c r="Q45" t="n">
-        <v>1464.547700482551</v>
+        <v>1575.738877341621</v>
       </c>
       <c r="R45" t="n">
-        <v>975.3822486720667</v>
+        <v>1575.738877341621</v>
       </c>
       <c r="S45" t="n">
-        <v>829.679460448388</v>
+        <v>1575.738877341621</v>
       </c>
       <c r="T45" t="n">
-        <v>829.679460448388</v>
+        <v>1575.738877341621</v>
       </c>
       <c r="U45" t="n">
-        <v>829.679460448388</v>
+        <v>1235.122352331332</v>
       </c>
       <c r="V45" t="n">
-        <v>829.679460448388</v>
+        <v>1235.122352331332</v>
       </c>
       <c r="W45" t="n">
-        <v>829.679460448388</v>
+        <v>1235.122352331332</v>
       </c>
       <c r="X45" t="n">
-        <v>829.679460448388</v>
+        <v>1235.122352331332</v>
       </c>
       <c r="Y45" t="n">
-        <v>489.89017482603</v>
+        <v>895.3330667089735</v>
       </c>
     </row>
     <row r="46">
@@ -7964,28 +7964,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>703.2232106068765</v>
       </c>
       <c r="N2" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O2" t="n">
         <v>895.2478695740924</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2870600406814136</v>
+        <v>825.2870600406815</v>
       </c>
       <c r="Q2" t="n">
-        <v>556.6053155630374</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8201,28 +8201,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>589.3681668165993</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>1060.271045550332</v>
+        <v>703.2232106068765</v>
       </c>
       <c r="N5" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
-        <v>70.24786957409245</v>
+        <v>895.2478695740924</v>
       </c>
       <c r="P5" t="n">
         <v>825.2870600406815</v>
       </c>
       <c r="Q5" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8444,22 +8444,22 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>194.106436475533</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N8" t="n">
-        <v>1096.663422488788</v>
+        <v>538.7493879302478</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>895.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>825.2870600406815</v>
       </c>
       <c r="Q8" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,7 +8675,7 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K11" t="n">
         <v>716.8751175230994</v>
@@ -8684,19 +8684,19 @@
         <v>825</v>
       </c>
       <c r="M11" t="n">
-        <v>1048.791946444818</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N11" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>895.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>146.6258379151924</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8918,7 +8918,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,13 +8927,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>895.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
       </c>
       <c r="Q14" t="n">
-        <v>366.9291208030185</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9155,7 +9155,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
@@ -9164,7 +9164,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>646.3249171075372</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
         <v>0.2870600406814136</v>
@@ -9392,7 +9392,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>825</v>
+        <v>589.3681668165957</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9404,10 +9404,10 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
-        <v>146.6258379151924</v>
+        <v>825.2870600406853</v>
       </c>
       <c r="Q20" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R20" t="n">
         <v>294.54111633436</v>
@@ -9626,25 +9626,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>158.9610829645514</v>
       </c>
       <c r="L23" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N23" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>70.24786957409245</v>
+        <v>895.2478695740963</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>825.2870600406853</v>
       </c>
       <c r="Q23" t="n">
-        <v>366.9291208030185</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9863,10 +9863,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>391.1018701982561</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,13 +9875,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>849.2478695741067</v>
+        <v>80.44523330718953</v>
       </c>
       <c r="P26" t="n">
-        <v>779.2870600406958</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10097,13 +10097,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>12.52635857576362</v>
       </c>
       <c r="L29" t="n">
-        <v>344.3371094908716</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
         <v>1060.271045550332</v>
@@ -10112,13 +10112,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>70.24786957409245</v>
+        <v>849.2478695741081</v>
       </c>
       <c r="P29" t="n">
-        <v>779.2870600407044</v>
+        <v>779.2870600406972</v>
       </c>
       <c r="Q29" t="n">
-        <v>615.8520732695737</v>
+        <v>563.9245545257386</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10340,19 +10340,19 @@
         <v>0</v>
       </c>
       <c r="L32" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>625.6081550412002</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>70.24786957409245</v>
+        <v>849.2478695741113</v>
       </c>
       <c r="P32" t="n">
-        <v>779.2870600407076</v>
+        <v>344.6241695315583</v>
       </c>
       <c r="Q32" t="n">
         <v>615.8520732695737</v>
@@ -10574,22 +10574,22 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>716.8751175230994</v>
+        <v>184.7515739097761</v>
       </c>
       <c r="L35" t="n">
-        <v>224.1859859892149</v>
+        <v>0</v>
       </c>
       <c r="M35" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N35" t="n">
-        <v>1096.663422488788</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O35" t="n">
-        <v>252.5238755526707</v>
+        <v>849.2478695741277</v>
       </c>
       <c r="P35" t="n">
-        <v>0.2870600406814136</v>
+        <v>779.2870600407167</v>
       </c>
       <c r="Q35" t="n">
         <v>615.8520732695737</v>
@@ -10808,13 +10808,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>162.3481635529014</v>
       </c>
       <c r="M38" t="n">
         <v>1060.271045550332</v>
@@ -10823,7 +10823,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>476.9969215825676</v>
+        <v>709.9104883707344</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>35.04300624509033</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>629.6118281519554</v>
+        <v>331.8107509150501</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
-        <v>70.24786957409245</v>
+        <v>849.2478695741722</v>
       </c>
       <c r="P41" t="n">
-        <v>779.2870600407758</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>331.8107509150018</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>526.2062816409988</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N44" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O44" t="n">
-        <v>849.2478695742204</v>
+        <v>849.2478695742059</v>
       </c>
       <c r="P44" t="n">
         <v>0.2870600406814136</v>
@@ -23232,13 +23232,13 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -23274,22 +23274,22 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>155.4060936691876</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>13.6915729871842</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -23384,10 +23384,10 @@
         <v>62.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>55.98090483695654</v>
@@ -23399,7 +23399,7 @@
         <v>20.04387284153003</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -23411,7 +23411,7 @@
         <v>63.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
         <v>295.6316114025499</v>
@@ -23420,10 +23420,10 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>381.4778574518667</v>
       </c>
       <c r="P13" t="n">
-        <v>116.5271618994215</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
         <v>500.839266425598</v>
@@ -23444,7 +23444,7 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>22.44364543010755</v>
@@ -23645,10 +23645,10 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>12.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L16" t="n">
-        <v>147.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
         <v>244.6316114025499</v>
@@ -23657,10 +23657,10 @@
         <v>295.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>21.99586562531675</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>268.4377472870943</v>
       </c>
       <c r="Q16" t="n">
         <v>449.839266425598</v>
@@ -23669,7 +23669,7 @@
         <v>450.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>86.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23891,16 +23891,16 @@
         <v>244.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>295.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
         <v>364.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>402.5746432435847</v>
       </c>
       <c r="Q19" t="n">
-        <v>107.3895679718998</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
         <v>450.6021279811511</v>
@@ -24131,16 +24131,16 @@
         <v>295.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>364.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>21.99586562531675</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
         <v>449.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>450.6021279811511</v>
+        <v>108.1524295274529</v>
       </c>
       <c r="S22" t="n">
         <v>86.37347970285543</v>
@@ -24335,7 +24335,7 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>9.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>4.98090483695654</v>
@@ -24362,25 +24362,25 @@
         <v>147.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>244.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>295.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>364.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>21.99586562531675</v>
+        <v>411.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>449.839266425598</v>
+        <v>343.1334079257305</v>
       </c>
       <c r="R25" t="n">
         <v>450.6021279811511</v>
       </c>
       <c r="S25" t="n">
-        <v>86.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>11.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -24408,13 +24408,13 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>256.9993129555745</v>
+        <v>18.4513351124194</v>
       </c>
       <c r="C26" t="n">
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>179.3632896068686</v>
@@ -24423,10 +24423,10 @@
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>116.545820432575</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24462,7 +24462,7 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
         <v>0</v>
@@ -24566,10 +24566,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>60.53621805555548</v>
@@ -24581,10 +24581,10 @@
         <v>49.38285596774193</v>
       </c>
       <c r="G28" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>3.77112610161862</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -24593,7 +24593,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>63.52077380114304</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>198.5476281577792</v>
@@ -24608,10 +24608,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
-        <v>462.4478973282775</v>
+        <v>309.9308555272179</v>
       </c>
       <c r="Q28" t="n">
-        <v>160.0624669370704</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24833,7 +24833,7 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>134.5476281577792</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
@@ -24851,10 +24851,10 @@
         <v>436.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>250.211197321625</v>
+        <v>42.29008946099037</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>73.37347970285543</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -25076,16 +25076,16 @@
         <v>231.6316114025499</v>
       </c>
       <c r="N34" t="n">
-        <v>282.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>277.604002638495</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>122.9498114845819</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>436.839266425598</v>
       </c>
       <c r="R34" t="n">
         <v>437.6021279811511</v>
@@ -25316,16 +25316,16 @@
         <v>282.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>351.445564079015</v>
+        <v>277.604002638495</v>
       </c>
       <c r="P37" t="n">
-        <v>363.7605665406311</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>437.6021279811511</v>
       </c>
       <c r="S37" t="n">
         <v>73.37347970285543</v>
@@ -25544,25 +25544,25 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>134.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M40" t="n">
         <v>231.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>122.9498114845819</v>
+        <v>282.1850752716849</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>351.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>398.4478973282775</v>
       </c>
       <c r="Q40" t="n">
-        <v>436.839266425598</v>
+        <v>99.8602973701328</v>
       </c>
       <c r="R40" t="n">
-        <v>437.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>73.37347970285543</v>
@@ -25593,10 +25593,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>210.3035241546127</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>271.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D41" t="n">
         <v>232.3391557398498</v>
@@ -25605,13 +25605,13 @@
         <v>226.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>226.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>225.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>230.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25647,13 +25647,13 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>379.2663052465318</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>451.8510241668239</v>
       </c>
       <c r="W41" t="n">
         <v>0</v>
@@ -25662,7 +25662,7 @@
         <v>0</v>
       </c>
       <c r="Y41" t="n">
-        <v>0</v>
+        <v>333.3174326828064</v>
       </c>
     </row>
     <row r="42">
@@ -25675,10 +25675,10 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>183.0999124455193</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>169.9376868977026</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
@@ -25690,7 +25690,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>154.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -25720,19 +25720,19 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>369.2737972923793</v>
+        <v>333.897397187038</v>
       </c>
       <c r="S42" t="n">
-        <v>288.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T42" t="n">
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>222.2103597601867</v>
       </c>
       <c r="V42" t="n">
-        <v>223.5873547426672</v>
+        <v>0</v>
       </c>
       <c r="W42" t="n">
         <v>0</v>
@@ -25741,7 +25741,7 @@
         <v>0</v>
       </c>
       <c r="Y42" t="n">
-        <v>0</v>
+        <v>221.3913927661343</v>
       </c>
     </row>
     <row r="43">
@@ -25769,7 +25769,7 @@
         <v>67.04387284153003</v>
       </c>
       <c r="H43" t="n">
-        <v>50.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -25799,13 +25799,13 @@
         <v>547.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>548.6021279811511</v>
+        <v>463.6642864844748</v>
       </c>
       <c r="S43" t="n">
         <v>184.3734797028554</v>
       </c>
       <c r="T43" t="n">
-        <v>32.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U43" t="n">
         <v>0</v>
@@ -25836,19 +25836,19 @@
         <v>386.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>347.3391557398498</v>
       </c>
       <c r="E44" t="n">
         <v>341.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>341.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>340.7573722870162</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>345.0096587035274</v>
       </c>
       <c r="I44" t="n">
         <v>87.08115968268461</v>
@@ -25878,28 +25878,28 @@
         <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>187.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>39.82666247030596</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>523.6755817285639</v>
       </c>
       <c r="U44" t="n">
-        <v>586.2212965486107</v>
+        <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>566.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
         <v>575.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>362.0853153603288</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>448.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -25909,7 +25909,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>321.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C45" t="n">
         <v>298.0999124455193</v>
@@ -25918,7 +25918,7 @@
         <v>284.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>279.6720972219126</v>
+        <v>45.71380501277656</v>
       </c>
       <c r="F45" t="n">
         <v>276.6362423378769</v>
@@ -25930,7 +25930,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>154.1263858913485</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25954,19 +25954,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>110.0792650904796</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>484.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>259.3182396231694</v>
+        <v>403.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>342.3577652175138</v>
       </c>
       <c r="U45" t="n">
-        <v>337.2103597601867</v>
+        <v>0</v>
       </c>
       <c r="V45" t="n">
         <v>351.5106671915202</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4040016.585741563</v>
+        <v>4040016.585741564</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5013999.009602254</v>
+        <v>5013999.009602255</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5987981.433462942</v>
+        <v>5987981.433462943</v>
       </c>
     </row>
     <row r="8">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7935946.281184313</v>
+        <v>7935946.281184315</v>
       </c>
     </row>
     <row r="10">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>10784906.7846262</v>
+        <v>10784906.78462619</v>
       </c>
     </row>
     <row r="13">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14061819.05786948</v>
+        <v>14061819.05786949</v>
       </c>
     </row>
   </sheetData>
@@ -26281,13 +26281,13 @@
         <v>1072955.698812016</v>
       </c>
       <c r="F2" t="n">
-        <v>1156604.128334571</v>
+        <v>1156604.128334572</v>
       </c>
       <c r="G2" t="n">
         <v>1156604.128334571</v>
       </c>
       <c r="H2" t="n">
-        <v>1156604.12833457</v>
+        <v>1156604.128334571</v>
       </c>
       <c r="I2" t="n">
         <v>1156604.128334571</v>
@@ -26299,7 +26299,7 @@
         <v>1163645.866822443</v>
       </c>
       <c r="L2" t="n">
-        <v>1163645.866822442</v>
+        <v>1163645.866822443</v>
       </c>
       <c r="M2" t="n">
         <v>1163645.866822443</v>
@@ -26308,10 +26308,10 @@
         <v>1163645.866822442</v>
       </c>
       <c r="O2" t="n">
-        <v>934970.2267645504</v>
+        <v>934970.2267645505</v>
       </c>
       <c r="P2" t="n">
-        <v>629337.776226926</v>
+        <v>629337.7762269258</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>553894.4209411235</v>
+        <v>549073.4019700913</v>
       </c>
       <c r="C4" t="n">
-        <v>552148.6767468527</v>
+        <v>547327.6577758205</v>
       </c>
       <c r="D4" t="n">
-        <v>550400.5643416208</v>
+        <v>545579.5453705885</v>
       </c>
       <c r="E4" t="n">
-        <v>475508.5085360265</v>
+        <v>470687.4895649942</v>
       </c>
       <c r="F4" t="n">
-        <v>523396.3864423812</v>
+        <v>518575.367471349</v>
       </c>
       <c r="G4" t="n">
-        <v>521737.4449277469</v>
+        <v>516916.4259567148</v>
       </c>
       <c r="H4" t="n">
-        <v>520076.2008969561</v>
+        <v>515255.1819259241</v>
       </c>
       <c r="I4" t="n">
-        <v>518412.637742535</v>
+        <v>513591.6187715029</v>
       </c>
       <c r="J4" t="n">
-        <v>464813.3679854202</v>
+        <v>460130.3405348168</v>
       </c>
       <c r="K4" t="n">
-        <v>523864.6016459742</v>
+        <v>519172.084144613</v>
       </c>
       <c r="L4" t="n">
-        <v>522143.8849986776</v>
+        <v>517451.3674973166</v>
       </c>
       <c r="M4" t="n">
-        <v>520420.7089809946</v>
+        <v>515728.1914796335</v>
       </c>
       <c r="N4" t="n">
-        <v>518695.0553227372</v>
+        <v>514002.5378213762</v>
       </c>
       <c r="O4" t="n">
-        <v>386080.5898356722</v>
+        <v>381397.5623850689</v>
       </c>
       <c r="P4" t="n">
-        <v>210633.5645263094</v>
+        <v>205950.5370757062</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>268326.1673748413</v>
+        <v>273147.1863458735</v>
       </c>
       <c r="C6" t="n">
-        <v>560471.9115691121</v>
+        <v>565292.9305401443</v>
       </c>
       <c r="D6" t="n">
-        <v>562220.0239743445</v>
+        <v>567041.0429453762</v>
       </c>
       <c r="E6" t="n">
-        <v>348371.6652759896</v>
+        <v>353192.6842470218</v>
       </c>
       <c r="F6" t="n">
-        <v>519044.69789219</v>
+        <v>523865.7168632229</v>
       </c>
       <c r="G6" t="n">
-        <v>561503.6394068243</v>
+        <v>566324.6583778564</v>
       </c>
       <c r="H6" t="n">
-        <v>563164.8834376143</v>
+        <v>567985.9024086471</v>
       </c>
       <c r="I6" t="n">
-        <v>564828.4465920364</v>
+        <v>569649.4655630685</v>
       </c>
       <c r="J6" t="n">
-        <v>114956.1654105956</v>
+        <v>119639.1928611987</v>
       </c>
       <c r="K6" t="n">
-        <v>476122.1241764685</v>
+        <v>480814.6416778295</v>
       </c>
       <c r="L6" t="n">
-        <v>569842.8408237644</v>
+        <v>574535.3583251259</v>
       </c>
       <c r="M6" t="n">
-        <v>571566.0168414481</v>
+        <v>576258.5343428091</v>
       </c>
       <c r="N6" t="n">
-        <v>573291.670499705</v>
+        <v>577984.188001066</v>
       </c>
       <c r="O6" t="n">
-        <v>436162.1549288782</v>
+        <v>440845.1823794816</v>
       </c>
       <c r="P6" t="n">
-        <v>366044.6647006166</v>
+        <v>370727.6921512196</v>
       </c>
     </row>
   </sheetData>
@@ -26987,7 +26987,7 @@
         <v>51</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27433,13 +27433,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C2" t="n">
         <v>400</v>
       </c>
       <c r="D2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>400</v>
@@ -27448,55 +27448,55 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="n">
         <v>400</v>
       </c>
-      <c r="H2" t="n">
+      <c r="T2" t="n">
         <v>400</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
-      </c>
-      <c r="K2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R2" t="n">
-        <v>250.8785988282945</v>
-      </c>
-      <c r="S2" t="n">
-        <v>13.82296829727017</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
       </c>
       <c r="U2" t="n">
         <v>400</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>400</v>
+        <v>264.7015671255647</v>
       </c>
       <c r="X2" t="n">
         <v>400</v>
@@ -27512,7 +27512,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
         <v>361.0999124455193</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>47.52172789347793</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,10 +27569,10 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="V3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
         <v>400</v>
@@ -27581,7 +27581,7 @@
         <v>400</v>
       </c>
       <c r="Y3" t="n">
-        <v>326.2223250290383</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="4">
@@ -27609,16 +27609,16 @@
         <v>400</v>
       </c>
       <c r="H4" t="n">
+        <v>379.6143391977814</v>
+      </c>
+      <c r="I4" t="n">
         <v>400</v>
-      </c>
-      <c r="I4" t="n">
-        <v>176.6334556201183</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27651,13 +27651,13 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>361.0740654228438</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
         <v>400</v>
       </c>
       <c r="X4" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
         <v>400</v>
@@ -27670,7 +27670,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114.6204074428801</v>
+        <v>400</v>
       </c>
       <c r="C5" t="n">
         <v>400</v>
@@ -27685,13 +27685,13 @@
         <v>400</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27733,7 +27733,7 @@
         <v>400</v>
       </c>
       <c r="W5" t="n">
-        <v>400</v>
+        <v>264.7015671255647</v>
       </c>
       <c r="X5" t="n">
         <v>400</v>
@@ -27758,7 +27758,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
         <v>339.6362423378769</v>
@@ -27767,7 +27767,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>217.1263858913485</v>
@@ -27803,7 +27803,7 @@
         <v>400</v>
       </c>
       <c r="T6" t="n">
-        <v>400</v>
+        <v>222.3801497007011</v>
       </c>
       <c r="U6" t="n">
         <v>400</v>
@@ -27815,7 +27815,7 @@
         <v>400</v>
       </c>
       <c r="X6" t="n">
-        <v>232.8841597361926</v>
+        <v>400</v>
       </c>
       <c r="Y6" t="n">
         <v>399.3913927661343</v>
@@ -27837,25 +27837,25 @@
         <v>400</v>
       </c>
       <c r="E7" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F7" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>312.9871637097752</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>400</v>
+        <v>176.6334556201183</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>400</v>
+        <v>288.520773801143</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>400</v>
       </c>
       <c r="U7" t="n">
+        <v>350.3511944106288</v>
+      </c>
+      <c r="V7" t="n">
+        <v>199.1703102162162</v>
+      </c>
+      <c r="W7" t="n">
         <v>400</v>
-      </c>
-      <c r="V7" t="n">
-        <v>400</v>
-      </c>
-      <c r="W7" t="n">
-        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27916,7 +27916,7 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>263.741808614586</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -27925,7 +27925,7 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>150.0811596826846</v>
@@ -27958,10 +27958,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>263.741808614585</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27989,13 +27989,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>193.9840721817119</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
@@ -28046,13 +28046,13 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>400</v>
+        <v>342.2743756165773</v>
       </c>
       <c r="Y9" t="n">
         <v>399.3913927661343</v>
@@ -28065,34 +28065,34 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>329.5243532418193</v>
+      </c>
+      <c r="C10" t="n">
+        <v>272.7252466480447</v>
+      </c>
+      <c r="D10" t="n">
+        <v>285.5362180555555</v>
+      </c>
+      <c r="E10" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F10" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G10" t="n">
+        <v>245.04387284153</v>
+      </c>
+      <c r="H10" t="n">
         <v>400</v>
       </c>
-      <c r="C10" t="n">
+      <c r="I10" t="n">
         <v>400</v>
       </c>
-      <c r="D10" t="n">
+      <c r="J10" t="n">
         <v>400</v>
       </c>
-      <c r="E10" t="n">
+      <c r="K10" t="n">
         <v>400</v>
-      </c>
-      <c r="F10" t="n">
-        <v>400</v>
-      </c>
-      <c r="G10" t="n">
-        <v>283.2613305956835</v>
-      </c>
-      <c r="H10" t="n">
-        <v>228.7711261016186</v>
-      </c>
-      <c r="I10" t="n">
-        <v>176.6334556201183</v>
-      </c>
-      <c r="J10" t="n">
-        <v>35.26894883590776</v>
-      </c>
-      <c r="K10" t="n">
-        <v>288.520773801143</v>
       </c>
       <c r="L10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28125,7 +28125,7 @@
         <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
         <v>400</v>
@@ -28134,7 +28134,7 @@
         <v>400</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>26.99048536749052</v>
+        <v>225</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28262,7 +28262,7 @@
         <v>225</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>26.99048536749038</v>
       </c>
       <c r="P12" t="n">
         <v>225</v>
@@ -28484,28 +28484,28 @@
         <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>96.37862156259374</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="M15" t="n">
-        <v>269.4578866530733</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>276</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
         <v>276</v>
@@ -28636,7 +28636,7 @@
         <v>276</v>
       </c>
       <c r="H17" t="n">
-        <v>275.7418086145858</v>
+        <v>276</v>
       </c>
       <c r="I17" t="n">
         <v>150.0811596826846</v>
@@ -28675,7 +28675,7 @@
         <v>276</v>
       </c>
       <c r="U17" t="n">
-        <v>276</v>
+        <v>275.7418086145852</v>
       </c>
       <c r="V17" t="n">
         <v>276</v>
@@ -28724,25 +28724,25 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>210.5842725444219</v>
+        <v>0</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>276</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>37.50500745394217</v>
       </c>
       <c r="P18" t="n">
-        <v>276</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>276</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>276</v>
@@ -28861,10 +28861,10 @@
         <v>276</v>
       </c>
       <c r="D20" t="n">
+        <v>276</v>
+      </c>
+      <c r="E20" t="n">
         <v>275.7418086145858</v>
-      </c>
-      <c r="E20" t="n">
-        <v>276</v>
       </c>
       <c r="F20" t="n">
         <v>276</v>
@@ -28955,31 +28955,31 @@
         <v>276</v>
       </c>
       <c r="I21" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>96.37862156259359</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>276</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>210.5842725444217</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>276</v>
       </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
       <c r="Q21" t="n">
-        <v>276</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
         <v>276</v>
@@ -29110,10 +29110,10 @@
         <v>276</v>
       </c>
       <c r="H23" t="n">
-        <v>276</v>
+        <v>275.7418086145858</v>
       </c>
       <c r="I23" t="n">
-        <v>149.8229682972704</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29192,23 +29192,23 @@
         <v>276</v>
       </c>
       <c r="I24" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
         <v>276</v>
       </c>
-      <c r="J24" t="n">
+      <c r="N24" t="n">
         <v>276</v>
       </c>
-      <c r="K24" t="n">
-        <v>210.5842725444217</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
       <c r="O24" t="n">
         <v>0</v>
       </c>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>276</v>
+        <v>269.4578866530733</v>
       </c>
       <c r="R24" t="n">
         <v>276</v>
@@ -29438,10 +29438,10 @@
         <v>225</v>
       </c>
       <c r="L27" t="n">
+        <v>19.11687125883913</v>
+      </c>
+      <c r="M27" t="n">
         <v>225</v>
-      </c>
-      <c r="M27" t="n">
-        <v>19.11687125883903</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29587,7 +29587,7 @@
         <v>289</v>
       </c>
       <c r="I29" t="n">
-        <v>146.3397682972702</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>250.8785988282945</v>
+        <v>247.13720744288</v>
       </c>
       <c r="S29" t="n">
         <v>289</v>
@@ -29666,7 +29666,7 @@
         <v>289</v>
       </c>
       <c r="I30" t="n">
-        <v>261.6249826760408</v>
+        <v>289</v>
       </c>
       <c r="J30" t="n">
         <v>0</v>
@@ -29675,7 +29675,7 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
@@ -29687,10 +29687,10 @@
         <v>0</v>
       </c>
       <c r="P30" t="n">
-        <v>289</v>
+        <v>88.54571758556126</v>
       </c>
       <c r="Q30" t="n">
-        <v>289</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R30" t="n">
         <v>289</v>
@@ -29824,7 +29824,7 @@
         <v>289</v>
       </c>
       <c r="I32" t="n">
-        <v>150.0811596826846</v>
+        <v>146.3397682972702</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29854,7 +29854,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S32" t="n">
-        <v>285.2586086145857</v>
+        <v>289</v>
       </c>
       <c r="T32" t="n">
         <v>289</v>
@@ -29903,7 +29903,7 @@
         <v>289</v>
       </c>
       <c r="I33" t="n">
-        <v>261.6249826760408</v>
+        <v>289</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -29915,7 +29915,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>261.624982676041</v>
       </c>
       <c r="N33" t="n">
         <v>0</v>
@@ -29924,7 +29924,7 @@
         <v>0</v>
       </c>
       <c r="P33" t="n">
-        <v>289</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
         <v>289</v>
@@ -30140,31 +30140,31 @@
         <v>289</v>
       </c>
       <c r="I36" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J36" t="n">
+        <v>160.419331694213</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
         <v>289</v>
       </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" t="n">
-        <v>261.624982676041</v>
-      </c>
-      <c r="O36" t="n">
-        <v>0</v>
-      </c>
       <c r="P36" t="n">
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>289</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R36" t="n">
         <v>289</v>
@@ -30340,13 +30340,13 @@
         <v>289</v>
       </c>
       <c r="W38" t="n">
-        <v>285.2586086145855</v>
+        <v>289</v>
       </c>
       <c r="X38" t="n">
         <v>289</v>
       </c>
       <c r="Y38" t="n">
-        <v>289</v>
+        <v>285.2586086145856</v>
       </c>
     </row>
     <row r="39">
@@ -30377,16 +30377,16 @@
         <v>289</v>
       </c>
       <c r="I39" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" t="n">
         <v>289</v>
       </c>
-      <c r="J39" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" t="n">
-        <v>261.6249826760411</v>
-      </c>
       <c r="L39" t="n">
-        <v>0</v>
+        <v>160.4193316942132</v>
       </c>
       <c r="M39" t="n">
         <v>0</v>
@@ -30401,7 +30401,7 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>289</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R39" t="n">
         <v>289</v>
@@ -30620,19 +30620,19 @@
         <v>178</v>
       </c>
       <c r="K42" t="n">
-        <v>178</v>
+        <v>139.7344266334506</v>
       </c>
       <c r="L42" t="n">
         <v>178</v>
       </c>
       <c r="M42" t="n">
-        <v>58.60567433317683</v>
+        <v>178</v>
       </c>
       <c r="N42" t="n">
         <v>178</v>
       </c>
       <c r="O42" t="n">
-        <v>178</v>
+        <v>0</v>
       </c>
       <c r="P42" t="n">
         <v>178</v>
@@ -30693,10 +30693,10 @@
         <v>178</v>
       </c>
       <c r="I43" t="n">
-        <v>176.6334556201183</v>
+        <v>178</v>
       </c>
       <c r="J43" t="n">
-        <v>35.26894883590776</v>
+        <v>178</v>
       </c>
       <c r="K43" t="n">
         <v>178</v>
@@ -30729,7 +30729,7 @@
         <v>178</v>
       </c>
       <c r="U43" t="n">
-        <v>150.9583912744579</v>
+        <v>178</v>
       </c>
       <c r="V43" t="n">
         <v>178</v>
@@ -30857,10 +30857,10 @@
         <v>63</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>63</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>63</v>
@@ -34743,28 +34743,28 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K2" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>516.0089179080152</v>
+        <v>158.9610829645592</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O2" t="n">
         <v>825</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="Q2" t="n">
-        <v>383.7826312355519</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34895,16 +34895,16 @@
         <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>171.2288738983814</v>
+        <v>150.8432130961628</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34937,13 +34937,13 @@
         <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>161.9037552066276</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>173.6271901612903</v>
       </c>
       <c r="X4" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y4" t="n">
         <v>112.5346471505376</v>
@@ -34980,28 +34980,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K5" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>589.3681668165993</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>516.0089179080152</v>
+        <v>158.9610829645592</v>
       </c>
       <c r="N5" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="P5" t="n">
         <v>825</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35123,25 +35123,25 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>84.21603760815664</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>223.3665443798817</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>111.479226198857</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
         <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
-        <v>249.0416087255421</v>
+        <v>199.3928031361708</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>173.6271901612903</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35223,22 +35223,22 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L8" t="n">
-        <v>194.106436475533</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>619.4144644189528</v>
+        <v>61.50042986041259</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>825</v>
       </c>
       <c r="P8" t="n">
         <v>825</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,34 +35351,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>42.41055290474068</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>38.21745775415347</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>364.7310511640923</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35411,7 +35411,7 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>173.6271901612903</v>
@@ -35420,7 +35420,7 @@
         <v>152.5563545698924</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230993</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
         <v>825</v>
       </c>
       <c r="M11" t="n">
-        <v>504.529818802501</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>146.338777874511</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>301.0818607161775</v>
+        <v>499.091375348687</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35548,7 +35548,7 @@
         <v>359.6265501086548</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>268.4475072702367</v>
       </c>
       <c r="P12" t="n">
         <v>338.6660045146532</v>
@@ -35697,7 +35697,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,13 +35706,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>194.1064364755331</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35770,28 +35770,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>221.5872278002695</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>467.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>274.091375348687</v>
+        <v>550.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>356.4079288175776</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N15" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>517.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q15" t="n">
-        <v>102.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35934,7 +35934,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>576.0770475334448</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
@@ -35943,7 +35943,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>576.0770475334447</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -36010,25 +36010,25 @@
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>401.6881271852132</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M18" t="n">
-        <v>86.95004216450428</v>
+        <v>362.9500421645043</v>
       </c>
       <c r="N18" t="n">
-        <v>134.6265501086548</v>
+        <v>410.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>278.9620293566886</v>
       </c>
       <c r="P18" t="n">
-        <v>389.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>102.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36171,7 +36171,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>825</v>
+        <v>589.3681668165957</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36183,10 +36183,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>146.338777874511</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="Q20" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -36241,31 +36241,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>58.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>401.688127185213</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L21" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M21" t="n">
-        <v>362.9500421645043</v>
+        <v>183.3286637270979</v>
       </c>
       <c r="N21" t="n">
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>241.4570219027464</v>
+        <v>517.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>113.6660045146532</v>
+        <v>389.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>102.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36405,25 +36405,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230993</v>
+        <v>158.9610829645514</v>
       </c>
       <c r="L23" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>825.0000000000039</v>
       </c>
       <c r="Q23" t="n">
-        <v>194.1064364755331</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,22 +36478,22 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>58.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>401.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>401.688127185213</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L24" t="n">
         <v>274.091375348687</v>
       </c>
       <c r="M24" t="n">
-        <v>86.95004216450428</v>
+        <v>362.9500421645043</v>
       </c>
       <c r="N24" t="n">
-        <v>134.6265501086548</v>
+        <v>410.6265501086548</v>
       </c>
       <c r="O24" t="n">
         <v>241.4570219027464</v>
@@ -36502,7 +36502,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>102.9207349095204</v>
+        <v>96.37862156259366</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,10 +36642,10 @@
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>391.1018701982561</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,13 +36654,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>779.0000000000143</v>
+        <v>10.19736373309708</v>
       </c>
       <c r="P26" t="n">
-        <v>779.0000000000143</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36724,10 +36724,10 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L27" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075261</v>
       </c>
       <c r="M27" t="n">
-        <v>106.0669134233433</v>
+        <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36876,13 +36876,13 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>182.2760059786471</v>
+        <v>12.52635857576363</v>
       </c>
       <c r="L29" t="n">
-        <v>779</v>
+        <v>616.9388964877305</v>
       </c>
       <c r="M29" t="n">
         <v>516.0089179080152</v>
@@ -36891,13 +36891,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>779.0000000000157</v>
       </c>
       <c r="P29" t="n">
-        <v>779.000000000023</v>
+        <v>779.0000000000157</v>
       </c>
       <c r="Q29" t="n">
-        <v>443.0293889420883</v>
+        <v>391.1018701982532</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -36952,7 +36952,7 @@
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>44.4985967846923</v>
+        <v>71.87361410865147</v>
       </c>
       <c r="J30" t="n">
         <v>125.2086062376757</v>
@@ -36961,7 +36961,7 @@
         <v>191.1038546407913</v>
       </c>
       <c r="L30" t="n">
-        <v>274.091375348687</v>
+        <v>563.0913753486871</v>
       </c>
       <c r="M30" t="n">
         <v>86.95004216450428</v>
@@ -36973,10 +36973,10 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>402.6660045146532</v>
+        <v>202.2117221002144</v>
       </c>
       <c r="Q30" t="n">
-        <v>115.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37116,22 +37116,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K32" t="n">
-        <v>616.9388964877458</v>
+        <v>182.2760059786919</v>
       </c>
       <c r="L32" t="n">
-        <v>779</v>
+        <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>81.34602739888294</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N32" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>779.0000000000189</v>
       </c>
       <c r="P32" t="n">
-        <v>779.0000000000261</v>
+        <v>779.0000000000189</v>
       </c>
       <c r="Q32" t="n">
         <v>443.0293889420883</v>
@@ -37189,7 +37189,7 @@
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>44.4985967846923</v>
+        <v>71.87361410865147</v>
       </c>
       <c r="J33" t="n">
         <v>125.2086062376757</v>
@@ -37201,7 +37201,7 @@
         <v>274.091375348687</v>
       </c>
       <c r="M33" t="n">
-        <v>86.95004216450428</v>
+        <v>348.5750248405453</v>
       </c>
       <c r="N33" t="n">
         <v>134.6265501086548</v>
@@ -37210,7 +37210,7 @@
         <v>241.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>402.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>115.9207349095204</v>
@@ -37353,22 +37353,22 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>779.0000000000002</v>
+        <v>779</v>
       </c>
       <c r="L35" t="n">
-        <v>779.0000000000001</v>
+        <v>22.69047039753866</v>
       </c>
       <c r="M35" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N35" t="n">
-        <v>619.4144644189528</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>182.2760059785783</v>
+        <v>779.0000000000352</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>779.0000000000352</v>
       </c>
       <c r="Q35" t="n">
         <v>443.0293889420883</v>
@@ -37426,10 +37426,10 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>71.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
-        <v>125.2086062376757</v>
+        <v>285.6279379318887</v>
       </c>
       <c r="K36" t="n">
         <v>191.1038546407913</v>
@@ -37441,16 +37441,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N36" t="n">
-        <v>396.2515327846959</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>530.4570219027464</v>
       </c>
       <c r="P36" t="n">
         <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>115.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37587,13 +37587,13 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>779.0000000000002</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
-        <v>554.5269539701297</v>
+        <v>778.9999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>516.0089179080152</v>
@@ -37602,7 +37602,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O38" t="n">
-        <v>406.7490520084751</v>
+        <v>639.6626187966419</v>
       </c>
       <c r="P38" t="n">
         <v>0</v>
@@ -37663,16 +37663,16 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>71.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
-        <v>452.7288373168324</v>
+        <v>480.1038546407913</v>
       </c>
       <c r="L39" t="n">
-        <v>274.091375348687</v>
+        <v>434.5107070429001</v>
       </c>
       <c r="M39" t="n">
         <v>86.95004216450428</v>
@@ -37687,7 +37687,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q39" t="n">
-        <v>115.9207349095204</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
         <v>0</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>629.6118281519554</v>
+        <v>331.8107509150501</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
-        <v>0</v>
+        <v>779.0000000000798</v>
       </c>
       <c r="P41" t="n">
-        <v>779.0000000000944</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37906,19 +37906,19 @@
         <v>303.2086062376757</v>
       </c>
       <c r="K42" t="n">
-        <v>369.1038546407913</v>
+        <v>330.8382812742419</v>
       </c>
       <c r="L42" t="n">
         <v>452.091375348687</v>
       </c>
       <c r="M42" t="n">
-        <v>145.5557164976811</v>
+        <v>264.9500421645043</v>
       </c>
       <c r="N42" t="n">
         <v>312.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>419.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P42" t="n">
         <v>291.6660045146532</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>1.366544379881727</v>
       </c>
       <c r="J43" t="n">
-        <v>0</v>
+        <v>142.7310511640922</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38015,7 +38015,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>27.04160872554206</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>331.8107509150018</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>526.2062816409988</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O44" t="n">
-        <v>779.000000000128</v>
+        <v>779.0000000001135</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -38143,10 +38143,10 @@
         <v>188.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>254.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L45" t="n">
-        <v>274.091375348687</v>
+        <v>337.091375348687</v>
       </c>
       <c r="M45" t="n">
         <v>149.9500421645043</v>
